--- a/03.QLDA/U284.xlsx
+++ b/03.QLDA/U284.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tool\Server_Leo_Nguyen\03.QLDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AMECC JSC\Amecc 2\00. Overall Report\03.QLDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C981E46D-1E02-45E1-AAE4-80766CA03739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F528CBA3-A77A-41D4-B8B1-8B9B74ADD471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,9 @@
     <definedName name="ㅋㅋㅋㅋㅋㅋㅋㅋㅋ" hidden="1">#REF!</definedName>
     <definedName name="ㅌㅊㅍㅌㅊㅍㅌㅋㅊㅍㅌ" hidden="1">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId2"/>
+    <pivotCache cacheId="94" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3449" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3450" uniqueCount="873">
   <si>
     <t>Gá lắp</t>
   </si>
@@ -2693,6 +2693,9 @@
   </si>
   <si>
     <t>U284-007-1</t>
+  </si>
+  <si>
+    <t>U284-003</t>
   </si>
 </sst>
 </file>
@@ -2700,11 +2703,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3057,7 +3060,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3145,28 +3148,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3187,19 +3190,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3221,13 +3224,13 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -3255,16 +3258,16 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3336,7 +3339,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Hiếu Nguyễn" refreshedDate="46293.62972986111" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="295" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46297.348200694447" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="295" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A3:BA298" sheet="Progress"/>
   </cacheSource>
@@ -3393,10 +3396,10 @@
     <cacheField name="T'Qty" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="156"/>
     </cacheField>
-    <cacheField name="U.Weight" numFmtId="164">
+    <cacheField name="U.Weight" numFmtId="43">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="33890.699999999997"/>
     </cacheField>
-    <cacheField name="T.Weight" numFmtId="164">
+    <cacheField name="T.Weight" numFmtId="43">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="33890.699999999997"/>
     </cacheField>
     <cacheField name="Profile" numFmtId="0">
@@ -3441,10 +3444,10 @@
     <cacheField name="DATE CPCL" numFmtId="14">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Hoàn thiện" numFmtId="165">
+    <cacheField name="Hoàn thiện" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="30501.629999999997"/>
     </cacheField>
-    <cacheField name="Còn lại" numFmtId="164">
+    <cacheField name="Còn lại" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="4443.8"/>
     </cacheField>
     <cacheField name="Kế hoạch Tháng" numFmtId="0">
@@ -3453,7 +3456,7 @@
     <cacheField name="Nhận Phôi" numFmtId="9">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Khối lượng" numFmtId="165">
+    <cacheField name="Khối lượng" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Ngày Gá" numFmtId="14">
@@ -3462,16 +3465,16 @@
     <cacheField name="SL Gá" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="55"/>
     </cacheField>
-    <cacheField name="KL Gá" numFmtId="164">
+    <cacheField name="KL Gá" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="33890.699999999997"/>
     </cacheField>
     <cacheField name="Ngày Hàn" numFmtId="14">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-07-03T00:00:00" maxDate="2026-09-27T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-07-03T00:00:00" maxDate="2026-10-01T00:00:00"/>
     </cacheField>
     <cacheField name="SL Hàn" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="55"/>
     </cacheField>
-    <cacheField name="KL Hàn" numFmtId="164">
+    <cacheField name="KL Hàn" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="33890.699999999997"/>
     </cacheField>
     <cacheField name="Ngày TH" numFmtId="14">
@@ -3480,7 +3483,7 @@
     <cacheField name="SL TH" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="KL TH" numFmtId="164">
+    <cacheField name="KL TH" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Số AFI" numFmtId="0">
@@ -3492,17 +3495,17 @@
     <cacheField name="SL NT" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="2"/>
     </cacheField>
-    <cacheField name="KL NT" numFmtId="164">
+    <cacheField name="KL NT" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="3463.5"/>
     </cacheField>
     <cacheField name="Ngày BG" numFmtId="14">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-09-16T00:00:00" maxDate="2026-09-17T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-09-16T00:00:00" maxDate="2026-10-01T00:00:00"/>
     </cacheField>
     <cacheField name="SL BG" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="2"/>
     </cacheField>
-    <cacheField name="KL BG" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="964.9"/>
+    <cacheField name="KL BG" numFmtId="43">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="3463.5"/>
     </cacheField>
     <cacheField name="Đơn vị nhận" numFmtId="0">
       <sharedItems containsBlank="1"/>
@@ -8117,17 +8120,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="136.15"/>
-    <n v="136.15"/>
+    <n v="245.07000000000002"/>
+    <n v="27.22999999999999"/>
     <m/>
     <m/>
     <n v="0"/>
     <d v="2026-09-21T00:00:00"/>
     <n v="1"/>
     <n v="272.3"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-28T00:00:00"/>
+    <n v="1"/>
+    <n v="272.3"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -8282,17 +8285,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="136.15"/>
-    <n v="136.15"/>
+    <n v="245.07000000000002"/>
+    <n v="27.22999999999999"/>
     <m/>
     <m/>
     <n v="0"/>
     <d v="2026-09-21T00:00:00"/>
     <n v="1"/>
     <n v="272.3"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-28T00:00:00"/>
+    <n v="1"/>
+    <n v="272.3"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -8392,17 +8395,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="136.15"/>
-    <n v="136.15"/>
+    <n v="245.07000000000002"/>
+    <n v="27.22999999999999"/>
     <m/>
     <m/>
     <n v="0"/>
     <d v="2026-09-21T00:00:00"/>
     <n v="1"/>
     <n v="272.3"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-28T00:00:00"/>
+    <n v="1"/>
+    <n v="272.3"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -8557,17 +8560,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="136.15"/>
-    <n v="136.15"/>
+    <n v="245.07000000000002"/>
+    <n v="27.22999999999999"/>
     <m/>
     <m/>
     <n v="0"/>
     <d v="2026-09-21T00:00:00"/>
     <n v="1"/>
     <n v="272.3"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-28T00:00:00"/>
+    <n v="1"/>
+    <n v="272.3"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -8722,17 +8725,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="136.15"/>
-    <n v="136.15"/>
+    <n v="245.07000000000002"/>
+    <n v="27.22999999999999"/>
     <m/>
     <m/>
     <n v="0"/>
     <d v="2026-09-21T00:00:00"/>
     <n v="1"/>
     <n v="272.3"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-28T00:00:00"/>
+    <n v="1"/>
+    <n v="272.3"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -8832,17 +8835,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="136.15"/>
-    <n v="136.15"/>
+    <n v="245.07000000000002"/>
+    <n v="27.22999999999999"/>
     <m/>
     <m/>
     <n v="0"/>
     <d v="2026-09-21T00:00:00"/>
     <n v="1"/>
     <n v="272.3"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-28T00:00:00"/>
+    <n v="1"/>
+    <n v="272.3"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -9052,17 +9055,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="309.45"/>
-    <n v="309.45"/>
+    <n v="557.01"/>
+    <n v="61.889999999999986"/>
     <m/>
     <m/>
     <n v="0"/>
     <d v="2026-09-21T00:00:00"/>
     <n v="1"/>
     <n v="618.9"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-28T00:00:00"/>
+    <n v="1"/>
+    <n v="618.9"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -9217,17 +9220,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="545"/>
-    <n v="545"/>
+    <n v="981"/>
+    <n v="109"/>
     <m/>
     <m/>
     <n v="0"/>
     <d v="2026-09-14T00:00:00"/>
     <n v="1"/>
     <n v="1090"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-30T00:00:00"/>
+    <n v="1"/>
+    <n v="1090"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -13342,17 +13345,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="151.35"/>
-    <n v="151.35"/>
+    <n v="272.43"/>
+    <n v="30.269999999999982"/>
     <m/>
     <m/>
     <n v="0"/>
     <d v="2026-09-25T00:00:00"/>
     <n v="2"/>
     <n v="302.7"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-30T00:00:00"/>
+    <n v="2"/>
+    <n v="302.7"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -13397,17 +13400,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="148.44999999999999"/>
-    <n v="148.44999999999999"/>
+    <n v="267.20999999999998"/>
+    <n v="29.689999999999998"/>
     <m/>
     <m/>
     <n v="0"/>
     <d v="2026-09-25T00:00:00"/>
     <n v="2"/>
     <n v="296.89999999999998"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-30T00:00:00"/>
+    <n v="2"/>
+    <n v="296.89999999999998"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -16880,11 +16883,11 @@
     <d v="2026-09-24T00:00:00"/>
     <n v="1"/>
     <n v="3463.5"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-30T00:00:00"/>
+    <n v="1"/>
+    <n v="3463.5"/>
     <s v="PAC"/>
-    <m/>
+    <s v="U284-003"/>
   </r>
   <r>
     <n v="244"/>
@@ -16990,11 +16993,11 @@
     <d v="2026-09-24T00:00:00"/>
     <n v="1"/>
     <n v="1004.9"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-28T00:00:00"/>
+    <n v="1"/>
+    <n v="1004.9"/>
     <s v="PAC"/>
-    <m/>
+    <s v="U284-007"/>
   </r>
   <r>
     <n v="246"/>
@@ -17467,17 +17470,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="1423.8"/>
-    <n v="1423.8"/>
+    <n v="2562.84"/>
+    <n v="284.75999999999976"/>
     <m/>
     <m/>
     <n v="0"/>
     <d v="2026-09-25T00:00:00"/>
     <n v="1"/>
     <n v="2847.6"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-28T00:00:00"/>
+    <n v="1"/>
+    <n v="2847.6"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -17522,17 +17525,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="1411.2"/>
-    <n v="1411.2"/>
+    <n v="2540.16"/>
+    <n v="282.24000000000024"/>
     <m/>
     <m/>
     <n v="0"/>
     <d v="2026-09-26T00:00:00"/>
     <n v="1"/>
     <n v="2822.4"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-28T00:00:00"/>
+    <n v="1"/>
+    <n v="2822.4"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -17650,11 +17653,11 @@
     <d v="2026-09-24T00:00:00"/>
     <n v="1"/>
     <n v="677.6"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-28T00:00:00"/>
+    <n v="1"/>
+    <n v="677.6"/>
     <s v="PAC"/>
-    <m/>
+    <s v="U284-007"/>
   </r>
   <r>
     <n v="258"/>
@@ -19750,7 +19753,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="94" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="BF3:BH8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="53">
     <pivotField showAll="0"/>
@@ -19802,27 +19805,27 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
@@ -19861,7 +19864,7 @@
   </colItems>
   <dataFields count="2">
     <dataField name="Sum of T.Weight" fld="15" baseField="1" baseItem="0"/>
-    <dataField name="Sum of KL Gá" fld="37" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Sum of KL Gá" fld="37" baseField="0" baseItem="0" numFmtId="43"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -20194,7 +20197,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:BH299"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelCol="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -20244,7 +20247,7 @@
     <col min="60" max="60" width="14.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="25.5" customHeight="1" thickTop="1">
+    <row r="1" spans="1:60" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str">
         <f>"DỰ ÁN:"&amp;B4</f>
         <v>DỰ ÁN:U284</v>
@@ -20315,7 +20318,7 @@
       <c r="BC1" s="48"/>
       <c r="BD1" s="48"/>
     </row>
-    <row r="2" spans="1:60" ht="25.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:60" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
@@ -20340,7 +20343,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="51">
         <f ca="1">IF(WEEKDAY(TODAY()-1)=1,TODAY()-2,TODAY()-1)</f>
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="T2" s="13" t="s">
         <v>40</v>
@@ -20374,11 +20377,11 @@
       <c r="AM2" s="15"/>
       <c r="AN2" s="67">
         <f>SUBTOTAL(9,AN4:AN298)</f>
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="AO2" s="68">
         <f>SUBTOTAL(9,AO4:AO298)</f>
-        <v>234841.49999999994</v>
+        <v>244453.79999999996</v>
       </c>
       <c r="AP2" s="15"/>
       <c r="AQ2" s="67">
@@ -20405,11 +20408,11 @@
       <c r="AW2" s="16"/>
       <c r="AX2" s="67">
         <f>SUBTOTAL(9,AX4:AX298)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY2" s="67">
         <f>SUBTOTAL(9,AY4:AY298)</f>
-        <v>3630.1000000000004</v>
+        <v>7093.5999999999995</v>
       </c>
       <c r="AZ2" s="17"/>
       <c r="BA2" s="18" t="str">
@@ -20420,7 +20423,7 @@
       <c r="BC2" s="48"/>
       <c r="BD2" s="48"/>
     </row>
-    <row r="3" spans="1:60" ht="27" customHeight="1" thickTop="1">
+    <row r="3" spans="1:60" ht="27" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>7</v>
       </c>
@@ -20599,7 +20602,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:60">
+    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
         <f>IF(B4="","",SUBTOTAL(3,$B$4:B4))</f>
         <v>1</v>
@@ -20728,7 +20731,7 @@
         <v>244453.8</v>
       </c>
     </row>
-    <row r="5" spans="1:60">
+    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A5" s="24">
         <f>IF(B5="","",SUBTOTAL(3,$B$4:B5))</f>
         <v>2</v>
@@ -20857,7 +20860,7 @@
         <v>244453.8</v>
       </c>
     </row>
-    <row r="6" spans="1:60">
+    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A6" s="24">
         <f>IF(B6="","",SUBTOTAL(3,$B$4:B6))</f>
         <v>3</v>
@@ -20986,7 +20989,7 @@
         <v>126330.99999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:60">
+    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A7" s="24">
         <f>IF(B7="","",SUBTOTAL(3,$B$4:B7))</f>
         <v>4</v>
@@ -21115,7 +21118,7 @@
         <v>118122.79999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:60">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A8" s="24">
         <f>IF(B8="","",SUBTOTAL(3,$B$4:B8))</f>
         <v>5</v>
@@ -21244,7 +21247,7 @@
         <v>244453.8</v>
       </c>
     </row>
-    <row r="9" spans="1:60">
+    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A9" s="24">
         <f>IF(B9="","",SUBTOTAL(3,$B$4:B9))</f>
         <v>6</v>
@@ -21364,7 +21367,7 @@
       <c r="BC9" s="71"/>
       <c r="BD9" s="71"/>
     </row>
-    <row r="10" spans="1:60">
+    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A10" s="24">
         <f>IF(B10="","",SUBTOTAL(3,$B$4:B10))</f>
         <v>7</v>
@@ -21484,7 +21487,7 @@
       <c r="BC10" s="71"/>
       <c r="BD10" s="71"/>
     </row>
-    <row r="11" spans="1:60">
+    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A11" s="24">
         <f>IF(B11="","",SUBTOTAL(3,$B$4:B11))</f>
         <v>8</v>
@@ -21604,7 +21607,7 @@
       <c r="BC11" s="71"/>
       <c r="BD11" s="71"/>
     </row>
-    <row r="12" spans="1:60">
+    <row r="12" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A12" s="24">
         <f>IF(B12="","",SUBTOTAL(3,$B$4:B12))</f>
         <v>9</v>
@@ -21724,7 +21727,7 @@
       <c r="BC12" s="71"/>
       <c r="BD12" s="71"/>
     </row>
-    <row r="13" spans="1:60">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A13" s="24">
         <f>IF(B13="","",SUBTOTAL(3,$B$4:B13))</f>
         <v>10</v>
@@ -21844,7 +21847,7 @@
       <c r="BC13" s="71"/>
       <c r="BD13" s="71"/>
     </row>
-    <row r="14" spans="1:60">
+    <row r="14" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A14" s="24">
         <f>IF(B14="","",SUBTOTAL(3,$B$4:B14))</f>
         <v>11</v>
@@ -21964,7 +21967,7 @@
       <c r="BC14" s="71"/>
       <c r="BD14" s="71"/>
     </row>
-    <row r="15" spans="1:60">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A15" s="24">
         <f>IF(B15="","",SUBTOTAL(3,$B$4:B15))</f>
         <v>12</v>
@@ -22084,7 +22087,7 @@
       <c r="BC15" s="71"/>
       <c r="BD15" s="71"/>
     </row>
-    <row r="16" spans="1:60">
+    <row r="16" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A16" s="24">
         <f>IF(B16="","",SUBTOTAL(3,$B$4:B16))</f>
         <v>13</v>
@@ -22204,7 +22207,7 @@
       <c r="BC16" s="71"/>
       <c r="BD16" s="71"/>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A17" s="24">
         <f>IF(B17="","",SUBTOTAL(3,$B$4:B17))</f>
         <v>14</v>
@@ -22324,7 +22327,7 @@
       <c r="BC17" s="71"/>
       <c r="BD17" s="71"/>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
         <f>IF(B18="","",SUBTOTAL(3,$B$4:B18))</f>
         <v>15</v>
@@ -22444,7 +22447,7 @@
       <c r="BC18" s="71"/>
       <c r="BD18" s="71"/>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A19" s="24">
         <f>IF(B19="","",SUBTOTAL(3,$B$4:B19))</f>
         <v>16</v>
@@ -22564,7 +22567,7 @@
       <c r="BC19" s="71"/>
       <c r="BD19" s="71"/>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A20" s="24">
         <f>IF(B20="","",SUBTOTAL(3,$B$4:B20))</f>
         <v>17</v>
@@ -22684,7 +22687,7 @@
       <c r="BC20" s="71"/>
       <c r="BD20" s="71"/>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A21" s="24">
         <f>IF(B21="","",SUBTOTAL(3,$B$4:B21))</f>
         <v>18</v>
@@ -22804,7 +22807,7 @@
       <c r="BC21" s="71"/>
       <c r="BD21" s="71"/>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A22" s="24">
         <f>IF(B22="","",SUBTOTAL(3,$B$4:B22))</f>
         <v>19</v>
@@ -22924,7 +22927,7 @@
       <c r="BC22" s="71"/>
       <c r="BD22" s="71"/>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A23" s="24">
         <f>IF(B23="","",SUBTOTAL(3,$B$4:B23))</f>
         <v>20</v>
@@ -23044,7 +23047,7 @@
       <c r="BC23" s="71"/>
       <c r="BD23" s="71"/>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A24" s="24">
         <f>IF(B24="","",SUBTOTAL(3,$B$4:B24))</f>
         <v>21</v>
@@ -23164,7 +23167,7 @@
       <c r="BC24" s="71"/>
       <c r="BD24" s="71"/>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A25" s="24">
         <f>IF(B25="","",SUBTOTAL(3,$B$4:B25))</f>
         <v>22</v>
@@ -23284,7 +23287,7 @@
       <c r="BC25" s="71"/>
       <c r="BD25" s="71"/>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A26" s="24">
         <f>IF(B26="","",SUBTOTAL(3,$B$4:B26))</f>
         <v>23</v>
@@ -23404,7 +23407,7 @@
       <c r="BC26" s="71"/>
       <c r="BD26" s="71"/>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A27" s="24">
         <f>IF(B27="","",SUBTOTAL(3,$B$4:B27))</f>
         <v>24</v>
@@ -23524,7 +23527,7 @@
       <c r="BC27" s="71"/>
       <c r="BD27" s="71"/>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A28" s="24">
         <f>IF(B28="","",SUBTOTAL(3,$B$4:B28))</f>
         <v>25</v>
@@ -23644,7 +23647,7 @@
       <c r="BC28" s="71"/>
       <c r="BD28" s="71"/>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A29" s="24">
         <f>IF(B29="","",SUBTOTAL(3,$B$4:B29))</f>
         <v>26</v>
@@ -23764,7 +23767,7 @@
       <c r="BC29" s="71"/>
       <c r="BD29" s="71"/>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A30" s="24">
         <f>IF(B30="","",SUBTOTAL(3,$B$4:B30))</f>
         <v>27</v>
@@ -23884,7 +23887,7 @@
       <c r="BC30" s="71"/>
       <c r="BD30" s="71"/>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A31" s="24">
         <f>IF(B31="","",SUBTOTAL(3,$B$4:B31))</f>
         <v>28</v>
@@ -24004,7 +24007,7 @@
       <c r="BC31" s="71"/>
       <c r="BD31" s="71"/>
     </row>
-    <row r="32" spans="1:56">
+    <row r="32" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A32" s="24">
         <f>IF(B32="","",SUBTOTAL(3,$B$4:B32))</f>
         <v>29</v>
@@ -24124,7 +24127,7 @@
       <c r="BC32" s="71"/>
       <c r="BD32" s="71"/>
     </row>
-    <row r="33" spans="1:56">
+    <row r="33" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A33" s="24">
         <f>IF(B33="","",SUBTOTAL(3,$B$4:B33))</f>
         <v>30</v>
@@ -24244,7 +24247,7 @@
       <c r="BC33" s="71"/>
       <c r="BD33" s="71"/>
     </row>
-    <row r="34" spans="1:56">
+    <row r="34" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A34" s="24">
         <f>IF(B34="","",SUBTOTAL(3,$B$4:B34))</f>
         <v>31</v>
@@ -24364,7 +24367,7 @@
       <c r="BC34" s="71"/>
       <c r="BD34" s="71"/>
     </row>
-    <row r="35" spans="1:56">
+    <row r="35" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A35" s="24">
         <f>IF(B35="","",SUBTOTAL(3,$B$4:B35))</f>
         <v>32</v>
@@ -24484,7 +24487,7 @@
       <c r="BC35" s="71"/>
       <c r="BD35" s="71"/>
     </row>
-    <row r="36" spans="1:56">
+    <row r="36" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A36" s="24">
         <f>IF(B36="","",SUBTOTAL(3,$B$4:B36))</f>
         <v>33</v>
@@ -24604,7 +24607,7 @@
       <c r="BC36" s="71"/>
       <c r="BD36" s="71"/>
     </row>
-    <row r="37" spans="1:56">
+    <row r="37" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A37" s="24">
         <f>IF(B37="","",SUBTOTAL(3,$B$4:B37))</f>
         <v>34</v>
@@ -24724,7 +24727,7 @@
       <c r="BC37" s="71"/>
       <c r="BD37" s="71"/>
     </row>
-    <row r="38" spans="1:56">
+    <row r="38" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A38" s="24">
         <f>IF(B38="","",SUBTOTAL(3,$B$4:B38))</f>
         <v>35</v>
@@ -24844,7 +24847,7 @@
       <c r="BC38" s="71"/>
       <c r="BD38" s="71"/>
     </row>
-    <row r="39" spans="1:56">
+    <row r="39" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A39" s="24">
         <f>IF(B39="","",SUBTOTAL(3,$B$4:B39))</f>
         <v>36</v>
@@ -24964,7 +24967,7 @@
       <c r="BC39" s="71"/>
       <c r="BD39" s="71"/>
     </row>
-    <row r="40" spans="1:56">
+    <row r="40" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A40" s="24">
         <f>IF(B40="","",SUBTOTAL(3,$B$4:B40))</f>
         <v>37</v>
@@ -25084,7 +25087,7 @@
       <c r="BC40" s="71"/>
       <c r="BD40" s="71"/>
     </row>
-    <row r="41" spans="1:56">
+    <row r="41" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A41" s="24">
         <f>IF(B41="","",SUBTOTAL(3,$B$4:B41))</f>
         <v>38</v>
@@ -25204,7 +25207,7 @@
       <c r="BC41" s="71"/>
       <c r="BD41" s="71"/>
     </row>
-    <row r="42" spans="1:56">
+    <row r="42" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A42" s="24">
         <f>IF(B42="","",SUBTOTAL(3,$B$4:B42))</f>
         <v>39</v>
@@ -25324,7 +25327,7 @@
       <c r="BC42" s="71"/>
       <c r="BD42" s="71"/>
     </row>
-    <row r="43" spans="1:56">
+    <row r="43" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A43" s="24">
         <f>IF(B43="","",SUBTOTAL(3,$B$4:B43))</f>
         <v>40</v>
@@ -25444,7 +25447,7 @@
       <c r="BC43" s="71"/>
       <c r="BD43" s="71"/>
     </row>
-    <row r="44" spans="1:56">
+    <row r="44" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A44" s="24">
         <f>IF(B44="","",SUBTOTAL(3,$B$4:B44))</f>
         <v>41</v>
@@ -25564,7 +25567,7 @@
       <c r="BC44" s="71"/>
       <c r="BD44" s="71"/>
     </row>
-    <row r="45" spans="1:56">
+    <row r="45" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A45" s="24">
         <f>IF(B45="","",SUBTOTAL(3,$B$4:B45))</f>
         <v>42</v>
@@ -25684,7 +25687,7 @@
       <c r="BC45" s="71"/>
       <c r="BD45" s="71"/>
     </row>
-    <row r="46" spans="1:56">
+    <row r="46" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A46" s="24">
         <f>IF(B46="","",SUBTOTAL(3,$B$4:B46))</f>
         <v>43</v>
@@ -25804,7 +25807,7 @@
       <c r="BC46" s="71"/>
       <c r="BD46" s="71"/>
     </row>
-    <row r="47" spans="1:56">
+    <row r="47" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A47" s="24">
         <f>IF(B47="","",SUBTOTAL(3,$B$4:B47))</f>
         <v>44</v>
@@ -25924,7 +25927,7 @@
       <c r="BC47" s="71"/>
       <c r="BD47" s="71"/>
     </row>
-    <row r="48" spans="1:56">
+    <row r="48" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A48" s="24">
         <f>IF(B48="","",SUBTOTAL(3,$B$4:B48))</f>
         <v>45</v>
@@ -26044,7 +26047,7 @@
       <c r="BC48" s="71"/>
       <c r="BD48" s="71"/>
     </row>
-    <row r="49" spans="1:56">
+    <row r="49" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A49" s="24">
         <f>IF(B49="","",SUBTOTAL(3,$B$4:B49))</f>
         <v>46</v>
@@ -26164,7 +26167,7 @@
       <c r="BC49" s="71"/>
       <c r="BD49" s="71"/>
     </row>
-    <row r="50" spans="1:56">
+    <row r="50" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A50" s="24">
         <f>IF(B50="","",SUBTOTAL(3,$B$4:B50))</f>
         <v>47</v>
@@ -26284,7 +26287,7 @@
       <c r="BC50" s="71"/>
       <c r="BD50" s="71"/>
     </row>
-    <row r="51" spans="1:56">
+    <row r="51" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A51" s="24">
         <f>IF(B51="","",SUBTOTAL(3,$B$4:B51))</f>
         <v>48</v>
@@ -26404,7 +26407,7 @@
       <c r="BC51" s="71"/>
       <c r="BD51" s="71"/>
     </row>
-    <row r="52" spans="1:56">
+    <row r="52" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A52" s="24">
         <f>IF(B52="","",SUBTOTAL(3,$B$4:B52))</f>
         <v>49</v>
@@ -26524,7 +26527,7 @@
       <c r="BC52" s="71"/>
       <c r="BD52" s="71"/>
     </row>
-    <row r="53" spans="1:56">
+    <row r="53" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A53" s="24">
         <f>IF(B53="","",SUBTOTAL(3,$B$4:B53))</f>
         <v>50</v>
@@ -26644,7 +26647,7 @@
       <c r="BC53" s="71"/>
       <c r="BD53" s="71"/>
     </row>
-    <row r="54" spans="1:56">
+    <row r="54" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A54" s="24">
         <f>IF(B54="","",SUBTOTAL(3,$B$4:B54))</f>
         <v>51</v>
@@ -26764,7 +26767,7 @@
       <c r="BC54" s="71"/>
       <c r="BD54" s="71"/>
     </row>
-    <row r="55" spans="1:56">
+    <row r="55" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A55" s="24">
         <f>IF(B55="","",SUBTOTAL(3,$B$4:B55))</f>
         <v>52</v>
@@ -26884,7 +26887,7 @@
       <c r="BC55" s="71"/>
       <c r="BD55" s="71"/>
     </row>
-    <row r="56" spans="1:56">
+    <row r="56" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A56" s="24">
         <f>IF(B56="","",SUBTOTAL(3,$B$4:B56))</f>
         <v>53</v>
@@ -27004,7 +27007,7 @@
       <c r="BC56" s="71"/>
       <c r="BD56" s="71"/>
     </row>
-    <row r="57" spans="1:56">
+    <row r="57" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A57" s="24">
         <f>IF(B57="","",SUBTOTAL(3,$B$4:B57))</f>
         <v>54</v>
@@ -27124,7 +27127,7 @@
       <c r="BC57" s="71"/>
       <c r="BD57" s="71"/>
     </row>
-    <row r="58" spans="1:56">
+    <row r="58" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A58" s="24">
         <f>IF(B58="","",SUBTOTAL(3,$B$4:B58))</f>
         <v>55</v>
@@ -27244,7 +27247,7 @@
       <c r="BC58" s="71"/>
       <c r="BD58" s="71"/>
     </row>
-    <row r="59" spans="1:56">
+    <row r="59" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A59" s="24">
         <f>IF(B59="","",SUBTOTAL(3,$B$4:B59))</f>
         <v>56</v>
@@ -27364,7 +27367,7 @@
       <c r="BC59" s="71"/>
       <c r="BD59" s="71"/>
     </row>
-    <row r="60" spans="1:56">
+    <row r="60" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A60" s="24">
         <f>IF(B60="","",SUBTOTAL(3,$B$4:B60))</f>
         <v>57</v>
@@ -27484,7 +27487,7 @@
       <c r="BC60" s="71"/>
       <c r="BD60" s="71"/>
     </row>
-    <row r="61" spans="1:56">
+    <row r="61" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A61" s="24">
         <f>IF(B61="","",SUBTOTAL(3,$B$4:B61))</f>
         <v>58</v>
@@ -27604,7 +27607,7 @@
       <c r="BC61" s="71"/>
       <c r="BD61" s="71"/>
     </row>
-    <row r="62" spans="1:56">
+    <row r="62" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A62" s="24">
         <f>IF(B62="","",SUBTOTAL(3,$B$4:B62))</f>
         <v>59</v>
@@ -27724,7 +27727,7 @@
       <c r="BC62" s="71"/>
       <c r="BD62" s="71"/>
     </row>
-    <row r="63" spans="1:56">
+    <row r="63" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A63" s="24">
         <f>IF(B63="","",SUBTOTAL(3,$B$4:B63))</f>
         <v>60</v>
@@ -27844,7 +27847,7 @@
       <c r="BC63" s="71"/>
       <c r="BD63" s="71"/>
     </row>
-    <row r="64" spans="1:56">
+    <row r="64" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A64" s="24">
         <f>IF(B64="","",SUBTOTAL(3,$B$4:B64))</f>
         <v>61</v>
@@ -27964,7 +27967,7 @@
       <c r="BC64" s="71"/>
       <c r="BD64" s="71"/>
     </row>
-    <row r="65" spans="1:56">
+    <row r="65" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A65" s="24">
         <f>IF(B65="","",SUBTOTAL(3,$B$4:B65))</f>
         <v>62</v>
@@ -28084,7 +28087,7 @@
       <c r="BC65" s="71"/>
       <c r="BD65" s="71"/>
     </row>
-    <row r="66" spans="1:56">
+    <row r="66" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A66" s="24">
         <f>IF(B66="","",SUBTOTAL(3,$B$4:B66))</f>
         <v>63</v>
@@ -28204,7 +28207,7 @@
       <c r="BC66" s="71"/>
       <c r="BD66" s="71"/>
     </row>
-    <row r="67" spans="1:56">
+    <row r="67" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A67" s="24">
         <f>IF(B67="","",SUBTOTAL(3,$B$4:B67))</f>
         <v>64</v>
@@ -28324,7 +28327,7 @@
       <c r="BC67" s="71"/>
       <c r="BD67" s="71"/>
     </row>
-    <row r="68" spans="1:56">
+    <row r="68" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A68" s="24">
         <f>IF(B68="","",SUBTOTAL(3,$B$4:B68))</f>
         <v>65</v>
@@ -28444,7 +28447,7 @@
       <c r="BC68" s="71"/>
       <c r="BD68" s="71"/>
     </row>
-    <row r="69" spans="1:56">
+    <row r="69" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A69" s="24">
         <f>IF(B69="","",SUBTOTAL(3,$B$4:B69))</f>
         <v>66</v>
@@ -28564,7 +28567,7 @@
       <c r="BC69" s="71"/>
       <c r="BD69" s="71"/>
     </row>
-    <row r="70" spans="1:56">
+    <row r="70" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A70" s="24">
         <f>IF(B70="","",SUBTOTAL(3,$B$4:B70))</f>
         <v>67</v>
@@ -28684,7 +28687,7 @@
       <c r="BC70" s="71"/>
       <c r="BD70" s="71"/>
     </row>
-    <row r="71" spans="1:56">
+    <row r="71" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A71" s="24">
         <f>IF(B71="","",SUBTOTAL(3,$B$4:B71))</f>
         <v>68</v>
@@ -28804,7 +28807,7 @@
       <c r="BC71" s="71"/>
       <c r="BD71" s="71"/>
     </row>
-    <row r="72" spans="1:56">
+    <row r="72" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A72" s="24">
         <f>IF(B72="","",SUBTOTAL(3,$B$4:B72))</f>
         <v>69</v>
@@ -28924,7 +28927,7 @@
       <c r="BC72" s="71"/>
       <c r="BD72" s="71"/>
     </row>
-    <row r="73" spans="1:56">
+    <row r="73" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A73" s="24">
         <f>IF(B73="","",SUBTOTAL(3,$B$4:B73))</f>
         <v>70</v>
@@ -29044,7 +29047,7 @@
       <c r="BC73" s="71"/>
       <c r="BD73" s="71"/>
     </row>
-    <row r="74" spans="1:56">
+    <row r="74" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A74" s="24">
         <f>IF(B74="","",SUBTOTAL(3,$B$4:B74))</f>
         <v>71</v>
@@ -29164,7 +29167,7 @@
       <c r="BC74" s="71"/>
       <c r="BD74" s="71"/>
     </row>
-    <row r="75" spans="1:56">
+    <row r="75" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A75" s="24">
         <f>IF(B75="","",SUBTOTAL(3,$B$4:B75))</f>
         <v>72</v>
@@ -29284,7 +29287,7 @@
       <c r="BC75" s="71"/>
       <c r="BD75" s="71"/>
     </row>
-    <row r="76" spans="1:56">
+    <row r="76" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A76" s="24">
         <f>IF(B76="","",SUBTOTAL(3,$B$4:B76))</f>
         <v>73</v>
@@ -29404,7 +29407,7 @@
       <c r="BC76" s="71"/>
       <c r="BD76" s="71"/>
     </row>
-    <row r="77" spans="1:56">
+    <row r="77" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A77" s="24">
         <f>IF(B77="","",SUBTOTAL(3,$B$4:B77))</f>
         <v>74</v>
@@ -29524,7 +29527,7 @@
       <c r="BC77" s="71"/>
       <c r="BD77" s="71"/>
     </row>
-    <row r="78" spans="1:56">
+    <row r="78" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A78" s="24">
         <f>IF(B78="","",SUBTOTAL(3,$B$4:B78))</f>
         <v>75</v>
@@ -29644,7 +29647,7 @@
       <c r="BC78" s="71"/>
       <c r="BD78" s="71"/>
     </row>
-    <row r="79" spans="1:56">
+    <row r="79" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A79" s="24">
         <f>IF(B79="","",SUBTOTAL(3,$B$4:B79))</f>
         <v>76</v>
@@ -29764,7 +29767,7 @@
       <c r="BC79" s="71"/>
       <c r="BD79" s="71"/>
     </row>
-    <row r="80" spans="1:56">
+    <row r="80" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A80" s="24">
         <f>IF(B80="","",SUBTOTAL(3,$B$4:B80))</f>
         <v>77</v>
@@ -29884,7 +29887,7 @@
       <c r="BC80" s="71"/>
       <c r="BD80" s="71"/>
     </row>
-    <row r="81" spans="1:56">
+    <row r="81" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A81" s="24">
         <f>IF(B81="","",SUBTOTAL(3,$B$4:B81))</f>
         <v>78</v>
@@ -30004,7 +30007,7 @@
       <c r="BC81" s="71"/>
       <c r="BD81" s="71"/>
     </row>
-    <row r="82" spans="1:56">
+    <row r="82" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A82" s="24">
         <f>IF(B82="","",SUBTOTAL(3,$B$4:B82))</f>
         <v>79</v>
@@ -30124,7 +30127,7 @@
       <c r="BC82" s="71"/>
       <c r="BD82" s="71"/>
     </row>
-    <row r="83" spans="1:56">
+    <row r="83" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A83" s="24">
         <f>IF(B83="","",SUBTOTAL(3,$B$4:B83))</f>
         <v>80</v>
@@ -30252,7 +30255,7 @@
       <c r="BC83" s="71"/>
       <c r="BD83" s="71"/>
     </row>
-    <row r="84" spans="1:56">
+    <row r="84" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A84" s="24">
         <f>IF(B84="","",SUBTOTAL(3,$B$4:B84))</f>
         <v>81</v>
@@ -30380,7 +30383,7 @@
       <c r="BC84" s="71"/>
       <c r="BD84" s="71"/>
     </row>
-    <row r="85" spans="1:56">
+    <row r="85" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A85" s="24">
         <f>IF(B85="","",SUBTOTAL(3,$B$4:B85))</f>
         <v>82</v>
@@ -30508,7 +30511,7 @@
       <c r="BC85" s="71"/>
       <c r="BD85" s="71"/>
     </row>
-    <row r="86" spans="1:56">
+    <row r="86" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A86" s="24">
         <f>IF(B86="","",SUBTOTAL(3,$B$4:B86))</f>
         <v>83</v>
@@ -30636,7 +30639,7 @@
       <c r="BC86" s="71"/>
       <c r="BD86" s="71"/>
     </row>
-    <row r="87" spans="1:56">
+    <row r="87" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A87" s="24">
         <f>IF(B87="","",SUBTOTAL(3,$B$4:B87))</f>
         <v>84</v>
@@ -30703,11 +30706,11 @@
       <c r="AD87" s="54"/>
       <c r="AE87" s="31">
         <f t="shared" si="19"/>
-        <v>136.15</v>
+        <v>245.07000000000002</v>
       </c>
       <c r="AF87" s="32">
         <f t="shared" si="20"/>
-        <v>136.15</v>
+        <v>27.22999999999999</v>
       </c>
       <c r="AG87" s="30"/>
       <c r="AH87" s="33"/>
@@ -30725,11 +30728,15 @@
         <f t="shared" si="22"/>
         <v>272.3</v>
       </c>
-      <c r="AM87" s="35"/>
-      <c r="AN87" s="30"/>
+      <c r="AM87" s="35">
+        <v>46293</v>
+      </c>
+      <c r="AN87" s="30">
+        <v>1</v>
+      </c>
       <c r="AO87" s="36">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>272.3</v>
       </c>
       <c r="AP87" s="35"/>
       <c r="AQ87" s="30"/>
@@ -30758,7 +30765,7 @@
       <c r="BC87" s="71"/>
       <c r="BD87" s="71"/>
     </row>
-    <row r="88" spans="1:56">
+    <row r="88" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A88" s="24">
         <f>IF(B88="","",SUBTOTAL(3,$B$4:B88))</f>
         <v>85</v>
@@ -30886,7 +30893,7 @@
       <c r="BC88" s="71"/>
       <c r="BD88" s="71"/>
     </row>
-    <row r="89" spans="1:56">
+    <row r="89" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A89" s="24">
         <f>IF(B89="","",SUBTOTAL(3,$B$4:B89))</f>
         <v>86</v>
@@ -31014,7 +31021,7 @@
       <c r="BC89" s="71"/>
       <c r="BD89" s="71"/>
     </row>
-    <row r="90" spans="1:56">
+    <row r="90" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A90" s="24">
         <f>IF(B90="","",SUBTOTAL(3,$B$4:B90))</f>
         <v>87</v>
@@ -31081,11 +31088,11 @@
       <c r="AD90" s="54"/>
       <c r="AE90" s="31">
         <f t="shared" si="19"/>
-        <v>136.15</v>
+        <v>245.07000000000002</v>
       </c>
       <c r="AF90" s="32">
         <f t="shared" si="20"/>
-        <v>136.15</v>
+        <v>27.22999999999999</v>
       </c>
       <c r="AG90" s="30"/>
       <c r="AH90" s="33"/>
@@ -31103,11 +31110,15 @@
         <f t="shared" si="22"/>
         <v>272.3</v>
       </c>
-      <c r="AM90" s="35"/>
-      <c r="AN90" s="30"/>
+      <c r="AM90" s="35">
+        <v>46293</v>
+      </c>
+      <c r="AN90" s="30">
+        <v>1</v>
+      </c>
       <c r="AO90" s="36">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>272.3</v>
       </c>
       <c r="AP90" s="35"/>
       <c r="AQ90" s="30"/>
@@ -31136,7 +31147,7 @@
       <c r="BC90" s="71"/>
       <c r="BD90" s="71"/>
     </row>
-    <row r="91" spans="1:56">
+    <row r="91" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A91" s="24">
         <f>IF(B91="","",SUBTOTAL(3,$B$4:B91))</f>
         <v>88</v>
@@ -31264,7 +31275,7 @@
       <c r="BC91" s="71"/>
       <c r="BD91" s="71"/>
     </row>
-    <row r="92" spans="1:56">
+    <row r="92" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A92" s="24">
         <f>IF(B92="","",SUBTOTAL(3,$B$4:B92))</f>
         <v>89</v>
@@ -31331,11 +31342,11 @@
       <c r="AD92" s="54"/>
       <c r="AE92" s="31">
         <f t="shared" si="19"/>
-        <v>136.15</v>
+        <v>245.07000000000002</v>
       </c>
       <c r="AF92" s="32">
         <f t="shared" si="20"/>
-        <v>136.15</v>
+        <v>27.22999999999999</v>
       </c>
       <c r="AG92" s="30"/>
       <c r="AH92" s="33"/>
@@ -31353,11 +31364,15 @@
         <f t="shared" si="22"/>
         <v>272.3</v>
       </c>
-      <c r="AM92" s="35"/>
-      <c r="AN92" s="30"/>
+      <c r="AM92" s="35">
+        <v>46293</v>
+      </c>
+      <c r="AN92" s="30">
+        <v>1</v>
+      </c>
       <c r="AO92" s="36">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>272.3</v>
       </c>
       <c r="AP92" s="35"/>
       <c r="AQ92" s="30"/>
@@ -31386,7 +31401,7 @@
       <c r="BC92" s="71"/>
       <c r="BD92" s="71"/>
     </row>
-    <row r="93" spans="1:56">
+    <row r="93" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A93" s="24">
         <f>IF(B93="","",SUBTOTAL(3,$B$4:B93))</f>
         <v>90</v>
@@ -31514,7 +31529,7 @@
       <c r="BC93" s="71"/>
       <c r="BD93" s="71"/>
     </row>
-    <row r="94" spans="1:56">
+    <row r="94" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A94" s="24">
         <f>IF(B94="","",SUBTOTAL(3,$B$4:B94))</f>
         <v>91</v>
@@ -31642,7 +31657,7 @@
       <c r="BC94" s="71"/>
       <c r="BD94" s="71"/>
     </row>
-    <row r="95" spans="1:56">
+    <row r="95" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A95" s="24">
         <f>IF(B95="","",SUBTOTAL(3,$B$4:B95))</f>
         <v>92</v>
@@ -31709,11 +31724,11 @@
       <c r="AD95" s="54"/>
       <c r="AE95" s="31">
         <f t="shared" si="19"/>
-        <v>136.15</v>
+        <v>245.07000000000002</v>
       </c>
       <c r="AF95" s="32">
         <f t="shared" si="20"/>
-        <v>136.15</v>
+        <v>27.22999999999999</v>
       </c>
       <c r="AG95" s="30"/>
       <c r="AH95" s="33"/>
@@ -31731,11 +31746,15 @@
         <f t="shared" si="22"/>
         <v>272.3</v>
       </c>
-      <c r="AM95" s="35"/>
-      <c r="AN95" s="30"/>
+      <c r="AM95" s="35">
+        <v>46293</v>
+      </c>
+      <c r="AN95" s="30">
+        <v>1</v>
+      </c>
       <c r="AO95" s="36">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>272.3</v>
       </c>
       <c r="AP95" s="35"/>
       <c r="AQ95" s="30"/>
@@ -31764,7 +31783,7 @@
       <c r="BC95" s="71"/>
       <c r="BD95" s="71"/>
     </row>
-    <row r="96" spans="1:56">
+    <row r="96" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A96" s="24">
         <f>IF(B96="","",SUBTOTAL(3,$B$4:B96))</f>
         <v>93</v>
@@ -31892,7 +31911,7 @@
       <c r="BC96" s="71"/>
       <c r="BD96" s="71"/>
     </row>
-    <row r="97" spans="1:56">
+    <row r="97" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A97" s="24">
         <f>IF(B97="","",SUBTOTAL(3,$B$4:B97))</f>
         <v>94</v>
@@ -32020,7 +32039,7 @@
       <c r="BC97" s="71"/>
       <c r="BD97" s="71"/>
     </row>
-    <row r="98" spans="1:56">
+    <row r="98" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A98" s="24">
         <f>IF(B98="","",SUBTOTAL(3,$B$4:B98))</f>
         <v>95</v>
@@ -32087,11 +32106,11 @@
       <c r="AD98" s="54"/>
       <c r="AE98" s="31">
         <f t="shared" si="19"/>
-        <v>136.15</v>
+        <v>245.07000000000002</v>
       </c>
       <c r="AF98" s="32">
         <f t="shared" si="20"/>
-        <v>136.15</v>
+        <v>27.22999999999999</v>
       </c>
       <c r="AG98" s="30"/>
       <c r="AH98" s="33"/>
@@ -32109,11 +32128,15 @@
         <f t="shared" si="22"/>
         <v>272.3</v>
       </c>
-      <c r="AM98" s="35"/>
-      <c r="AN98" s="30"/>
+      <c r="AM98" s="35">
+        <v>46293</v>
+      </c>
+      <c r="AN98" s="30">
+        <v>1</v>
+      </c>
       <c r="AO98" s="36">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>272.3</v>
       </c>
       <c r="AP98" s="35"/>
       <c r="AQ98" s="30"/>
@@ -32142,7 +32165,7 @@
       <c r="BC98" s="71"/>
       <c r="BD98" s="71"/>
     </row>
-    <row r="99" spans="1:56">
+    <row r="99" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A99" s="24">
         <f>IF(B99="","",SUBTOTAL(3,$B$4:B99))</f>
         <v>96</v>
@@ -32270,7 +32293,7 @@
       <c r="BC99" s="71"/>
       <c r="BD99" s="71"/>
     </row>
-    <row r="100" spans="1:56">
+    <row r="100" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A100" s="24">
         <f>IF(B100="","",SUBTOTAL(3,$B$4:B100))</f>
         <v>97</v>
@@ -32337,11 +32360,11 @@
       <c r="AD100" s="54"/>
       <c r="AE100" s="31">
         <f t="shared" si="19"/>
-        <v>136.15</v>
+        <v>245.07000000000002</v>
       </c>
       <c r="AF100" s="32">
         <f t="shared" si="20"/>
-        <v>136.15</v>
+        <v>27.22999999999999</v>
       </c>
       <c r="AG100" s="30"/>
       <c r="AH100" s="33"/>
@@ -32359,11 +32382,15 @@
         <f t="shared" si="22"/>
         <v>272.3</v>
       </c>
-      <c r="AM100" s="35"/>
-      <c r="AN100" s="30"/>
+      <c r="AM100" s="35">
+        <v>46293</v>
+      </c>
+      <c r="AN100" s="30">
+        <v>1</v>
+      </c>
       <c r="AO100" s="36">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>272.3</v>
       </c>
       <c r="AP100" s="35"/>
       <c r="AQ100" s="30"/>
@@ -32392,7 +32419,7 @@
       <c r="BC100" s="71"/>
       <c r="BD100" s="71"/>
     </row>
-    <row r="101" spans="1:56">
+    <row r="101" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A101" s="24">
         <f>IF(B101="","",SUBTOTAL(3,$B$4:B101))</f>
         <v>98</v>
@@ -32520,7 +32547,7 @@
       <c r="BC101" s="71"/>
       <c r="BD101" s="71"/>
     </row>
-    <row r="102" spans="1:56">
+    <row r="102" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A102" s="24">
         <f>IF(B102="","",SUBTOTAL(3,$B$4:B102))</f>
         <v>99</v>
@@ -32648,7 +32675,7 @@
       <c r="BC102" s="71"/>
       <c r="BD102" s="71"/>
     </row>
-    <row r="103" spans="1:56">
+    <row r="103" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A103" s="24">
         <f>IF(B103="","",SUBTOTAL(3,$B$4:B103))</f>
         <v>100</v>
@@ -32776,7 +32803,7 @@
       <c r="BC103" s="71"/>
       <c r="BD103" s="71"/>
     </row>
-    <row r="104" spans="1:56">
+    <row r="104" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A104" s="24">
         <f>IF(B104="","",SUBTOTAL(3,$B$4:B104))</f>
         <v>101</v>
@@ -32845,11 +32872,11 @@
       <c r="AD104" s="54"/>
       <c r="AE104" s="31">
         <f t="shared" si="19"/>
-        <v>309.45</v>
+        <v>557.01</v>
       </c>
       <c r="AF104" s="32">
         <f t="shared" si="20"/>
-        <v>309.45</v>
+        <v>61.889999999999986</v>
       </c>
       <c r="AG104" s="30"/>
       <c r="AH104" s="33"/>
@@ -32867,11 +32894,15 @@
         <f t="shared" si="22"/>
         <v>618.9</v>
       </c>
-      <c r="AM104" s="35"/>
-      <c r="AN104" s="30"/>
+      <c r="AM104" s="35">
+        <v>46293</v>
+      </c>
+      <c r="AN104" s="30">
+        <v>1</v>
+      </c>
       <c r="AO104" s="36">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>618.9</v>
       </c>
       <c r="AP104" s="35"/>
       <c r="AQ104" s="30"/>
@@ -32900,7 +32931,7 @@
       <c r="BC104" s="71"/>
       <c r="BD104" s="71"/>
     </row>
-    <row r="105" spans="1:56">
+    <row r="105" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A105" s="24">
         <f>IF(B105="","",SUBTOTAL(3,$B$4:B105))</f>
         <v>102</v>
@@ -33028,7 +33059,7 @@
       <c r="BC105" s="71"/>
       <c r="BD105" s="71"/>
     </row>
-    <row r="106" spans="1:56">
+    <row r="106" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A106" s="24">
         <f>IF(B106="","",SUBTOTAL(3,$B$4:B106))</f>
         <v>103</v>
@@ -33156,7 +33187,7 @@
       <c r="BC106" s="71"/>
       <c r="BD106" s="71"/>
     </row>
-    <row r="107" spans="1:56">
+    <row r="107" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A107" s="24">
         <f>IF(B107="","",SUBTOTAL(3,$B$4:B107))</f>
         <v>104</v>
@@ -33225,11 +33256,11 @@
       <c r="AD107" s="54"/>
       <c r="AE107" s="31">
         <f t="shared" si="19"/>
-        <v>545</v>
+        <v>981</v>
       </c>
       <c r="AF107" s="32">
         <f t="shared" si="20"/>
-        <v>545</v>
+        <v>109</v>
       </c>
       <c r="AG107" s="30"/>
       <c r="AH107" s="33"/>
@@ -33247,11 +33278,15 @@
         <f t="shared" si="22"/>
         <v>1090</v>
       </c>
-      <c r="AM107" s="35"/>
-      <c r="AN107" s="30"/>
+      <c r="AM107" s="35">
+        <v>46295</v>
+      </c>
+      <c r="AN107" s="30">
+        <v>1</v>
+      </c>
       <c r="AO107" s="36">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1090</v>
       </c>
       <c r="AP107" s="35"/>
       <c r="AQ107" s="30"/>
@@ -33280,7 +33315,7 @@
       <c r="BC107" s="71"/>
       <c r="BD107" s="71"/>
     </row>
-    <row r="108" spans="1:56">
+    <row r="108" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A108" s="24">
         <f>IF(B108="","",SUBTOTAL(3,$B$4:B108))</f>
         <v>105</v>
@@ -33400,7 +33435,7 @@
       <c r="BC108" s="71"/>
       <c r="BD108" s="71"/>
     </row>
-    <row r="109" spans="1:56">
+    <row r="109" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A109" s="24">
         <f>IF(B109="","",SUBTOTAL(3,$B$4:B109))</f>
         <v>106</v>
@@ -33520,7 +33555,7 @@
       <c r="BC109" s="71"/>
       <c r="BD109" s="71"/>
     </row>
-    <row r="110" spans="1:56">
+    <row r="110" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A110" s="24">
         <f>IF(B110="","",SUBTOTAL(3,$B$4:B110))</f>
         <v>107</v>
@@ -33640,7 +33675,7 @@
       <c r="BC110" s="71"/>
       <c r="BD110" s="71"/>
     </row>
-    <row r="111" spans="1:56">
+    <row r="111" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A111" s="24">
         <f>IF(B111="","",SUBTOTAL(3,$B$4:B111))</f>
         <v>108</v>
@@ -33760,7 +33795,7 @@
       <c r="BC111" s="71"/>
       <c r="BD111" s="71"/>
     </row>
-    <row r="112" spans="1:56">
+    <row r="112" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A112" s="24">
         <f>IF(B112="","",SUBTOTAL(3,$B$4:B112))</f>
         <v>109</v>
@@ -33880,7 +33915,7 @@
       <c r="BC112" s="71"/>
       <c r="BD112" s="71"/>
     </row>
-    <row r="113" spans="1:56">
+    <row r="113" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A113" s="24">
         <f>IF(B113="","",SUBTOTAL(3,$B$4:B113))</f>
         <v>110</v>
@@ -34000,7 +34035,7 @@
       <c r="BC113" s="71"/>
       <c r="BD113" s="71"/>
     </row>
-    <row r="114" spans="1:56">
+    <row r="114" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A114" s="24">
         <f>IF(B114="","",SUBTOTAL(3,$B$4:B114))</f>
         <v>111</v>
@@ -34120,7 +34155,7 @@
       <c r="BC114" s="71"/>
       <c r="BD114" s="71"/>
     </row>
-    <row r="115" spans="1:56">
+    <row r="115" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A115" s="24">
         <f>IF(B115="","",SUBTOTAL(3,$B$4:B115))</f>
         <v>112</v>
@@ -34240,7 +34275,7 @@
       <c r="BC115" s="71"/>
       <c r="BD115" s="71"/>
     </row>
-    <row r="116" spans="1:56">
+    <row r="116" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A116" s="24">
         <f>IF(B116="","",SUBTOTAL(3,$B$4:B116))</f>
         <v>113</v>
@@ -34360,7 +34395,7 @@
       <c r="BC116" s="71"/>
       <c r="BD116" s="71"/>
     </row>
-    <row r="117" spans="1:56">
+    <row r="117" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A117" s="24">
         <f>IF(B117="","",SUBTOTAL(3,$B$4:B117))</f>
         <v>114</v>
@@ -34480,7 +34515,7 @@
       <c r="BC117" s="71"/>
       <c r="BD117" s="71"/>
     </row>
-    <row r="118" spans="1:56">
+    <row r="118" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A118" s="24">
         <f>IF(B118="","",SUBTOTAL(3,$B$4:B118))</f>
         <v>115</v>
@@ -34600,7 +34635,7 @@
       <c r="BC118" s="71"/>
       <c r="BD118" s="71"/>
     </row>
-    <row r="119" spans="1:56">
+    <row r="119" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A119" s="24">
         <f>IF(B119="","",SUBTOTAL(3,$B$4:B119))</f>
         <v>116</v>
@@ -34720,7 +34755,7 @@
       <c r="BC119" s="71"/>
       <c r="BD119" s="71"/>
     </row>
-    <row r="120" spans="1:56">
+    <row r="120" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A120" s="24">
         <f>IF(B120="","",SUBTOTAL(3,$B$4:B120))</f>
         <v>117</v>
@@ -34840,7 +34875,7 @@
       <c r="BC120" s="71"/>
       <c r="BD120" s="71"/>
     </row>
-    <row r="121" spans="1:56">
+    <row r="121" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A121" s="24">
         <f>IF(B121="","",SUBTOTAL(3,$B$4:B121))</f>
         <v>118</v>
@@ -34960,7 +34995,7 @@
       <c r="BC121" s="71"/>
       <c r="BD121" s="71"/>
     </row>
-    <row r="122" spans="1:56">
+    <row r="122" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A122" s="24">
         <f>IF(B122="","",SUBTOTAL(3,$B$4:B122))</f>
         <v>119</v>
@@ -35080,7 +35115,7 @@
       <c r="BC122" s="71"/>
       <c r="BD122" s="71"/>
     </row>
-    <row r="123" spans="1:56">
+    <row r="123" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A123" s="24">
         <f>IF(B123="","",SUBTOTAL(3,$B$4:B123))</f>
         <v>120</v>
@@ -35200,7 +35235,7 @@
       <c r="BC123" s="71"/>
       <c r="BD123" s="71"/>
     </row>
-    <row r="124" spans="1:56">
+    <row r="124" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A124" s="24">
         <f>IF(B124="","",SUBTOTAL(3,$B$4:B124))</f>
         <v>121</v>
@@ -35320,7 +35355,7 @@
       <c r="BC124" s="71"/>
       <c r="BD124" s="71"/>
     </row>
-    <row r="125" spans="1:56">
+    <row r="125" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A125" s="24">
         <f>IF(B125="","",SUBTOTAL(3,$B$4:B125))</f>
         <v>122</v>
@@ -35440,7 +35475,7 @@
       <c r="BC125" s="71"/>
       <c r="BD125" s="71"/>
     </row>
-    <row r="126" spans="1:56">
+    <row r="126" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A126" s="24">
         <f>IF(B126="","",SUBTOTAL(3,$B$4:B126))</f>
         <v>123</v>
@@ -35560,7 +35595,7 @@
       <c r="BC126" s="71"/>
       <c r="BD126" s="71"/>
     </row>
-    <row r="127" spans="1:56">
+    <row r="127" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A127" s="24">
         <f>IF(B127="","",SUBTOTAL(3,$B$4:B127))</f>
         <v>124</v>
@@ -35680,7 +35715,7 @@
       <c r="BC127" s="71"/>
       <c r="BD127" s="71"/>
     </row>
-    <row r="128" spans="1:56">
+    <row r="128" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A128" s="24">
         <f>IF(B128="","",SUBTOTAL(3,$B$4:B128))</f>
         <v>125</v>
@@ -35800,7 +35835,7 @@
       <c r="BC128" s="71"/>
       <c r="BD128" s="71"/>
     </row>
-    <row r="129" spans="1:56">
+    <row r="129" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A129" s="24">
         <f>IF(B129="","",SUBTOTAL(3,$B$4:B129))</f>
         <v>126</v>
@@ -35920,7 +35955,7 @@
       <c r="BC129" s="71"/>
       <c r="BD129" s="71"/>
     </row>
-    <row r="130" spans="1:56">
+    <row r="130" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A130" s="24">
         <f>IF(B130="","",SUBTOTAL(3,$B$4:B130))</f>
         <v>127</v>
@@ -36040,7 +36075,7 @@
       <c r="BC130" s="71"/>
       <c r="BD130" s="71"/>
     </row>
-    <row r="131" spans="1:56">
+    <row r="131" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A131" s="24">
         <f>IF(B131="","",SUBTOTAL(3,$B$4:B131))</f>
         <v>128</v>
@@ -36160,7 +36195,7 @@
       <c r="BC131" s="71"/>
       <c r="BD131" s="71"/>
     </row>
-    <row r="132" spans="1:56">
+    <row r="132" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A132" s="24">
         <f>IF(B132="","",SUBTOTAL(3,$B$4:B132))</f>
         <v>129</v>
@@ -36280,7 +36315,7 @@
       <c r="BC132" s="71"/>
       <c r="BD132" s="71"/>
     </row>
-    <row r="133" spans="1:56">
+    <row r="133" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A133" s="24">
         <f>IF(B133="","",SUBTOTAL(3,$B$4:B133))</f>
         <v>130</v>
@@ -36400,7 +36435,7 @@
       <c r="BC133" s="71"/>
       <c r="BD133" s="71"/>
     </row>
-    <row r="134" spans="1:56">
+    <row r="134" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A134" s="24">
         <f>IF(B134="","",SUBTOTAL(3,$B$4:B134))</f>
         <v>131</v>
@@ -36520,7 +36555,7 @@
       <c r="BC134" s="71"/>
       <c r="BD134" s="71"/>
     </row>
-    <row r="135" spans="1:56">
+    <row r="135" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A135" s="24">
         <f>IF(B135="","",SUBTOTAL(3,$B$4:B135))</f>
         <v>132</v>
@@ -36640,7 +36675,7 @@
       <c r="BC135" s="71"/>
       <c r="BD135" s="71"/>
     </row>
-    <row r="136" spans="1:56">
+    <row r="136" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A136" s="24">
         <f>IF(B136="","",SUBTOTAL(3,$B$4:B136))</f>
         <v>133</v>
@@ -36760,7 +36795,7 @@
       <c r="BC136" s="71"/>
       <c r="BD136" s="71"/>
     </row>
-    <row r="137" spans="1:56">
+    <row r="137" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A137" s="24">
         <f>IF(B137="","",SUBTOTAL(3,$B$4:B137))</f>
         <v>134</v>
@@ -36880,7 +36915,7 @@
       <c r="BC137" s="71"/>
       <c r="BD137" s="71"/>
     </row>
-    <row r="138" spans="1:56">
+    <row r="138" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A138" s="24">
         <f>IF(B138="","",SUBTOTAL(3,$B$4:B138))</f>
         <v>135</v>
@@ -36998,7 +37033,7 @@
       <c r="BC138" s="71"/>
       <c r="BD138" s="71"/>
     </row>
-    <row r="139" spans="1:56">
+    <row r="139" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A139" s="24">
         <f>IF(B139="","",SUBTOTAL(3,$B$4:B139))</f>
         <v>136</v>
@@ -37116,7 +37151,7 @@
       <c r="BC139" s="71"/>
       <c r="BD139" s="71"/>
     </row>
-    <row r="140" spans="1:56">
+    <row r="140" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A140" s="24">
         <f>IF(B140="","",SUBTOTAL(3,$B$4:B140))</f>
         <v>137</v>
@@ -37234,7 +37269,7 @@
       <c r="BC140" s="71"/>
       <c r="BD140" s="71"/>
     </row>
-    <row r="141" spans="1:56">
+    <row r="141" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A141" s="24">
         <f>IF(B141="","",SUBTOTAL(3,$B$4:B141))</f>
         <v>138</v>
@@ -37352,7 +37387,7 @@
       <c r="BC141" s="71"/>
       <c r="BD141" s="71"/>
     </row>
-    <row r="142" spans="1:56">
+    <row r="142" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A142" s="24">
         <f>IF(B142="","",SUBTOTAL(3,$B$4:B142))</f>
         <v>139</v>
@@ -37470,7 +37505,7 @@
       <c r="BC142" s="71"/>
       <c r="BD142" s="71"/>
     </row>
-    <row r="143" spans="1:56">
+    <row r="143" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A143" s="24">
         <f>IF(B143="","",SUBTOTAL(3,$B$4:B143))</f>
         <v>140</v>
@@ -37588,7 +37623,7 @@
       <c r="BC143" s="71"/>
       <c r="BD143" s="71"/>
     </row>
-    <row r="144" spans="1:56">
+    <row r="144" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A144" s="24">
         <f>IF(B144="","",SUBTOTAL(3,$B$4:B144))</f>
         <v>141</v>
@@ -37706,7 +37741,7 @@
       <c r="BC144" s="71"/>
       <c r="BD144" s="71"/>
     </row>
-    <row r="145" spans="1:56">
+    <row r="145" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A145" s="24">
         <f>IF(B145="","",SUBTOTAL(3,$B$4:B145))</f>
         <v>142</v>
@@ -37824,7 +37859,7 @@
       <c r="BC145" s="71"/>
       <c r="BD145" s="71"/>
     </row>
-    <row r="146" spans="1:56">
+    <row r="146" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A146" s="24">
         <f>IF(B146="","",SUBTOTAL(3,$B$4:B146))</f>
         <v>143</v>
@@ -37942,7 +37977,7 @@
       <c r="BC146" s="71"/>
       <c r="BD146" s="71"/>
     </row>
-    <row r="147" spans="1:56">
+    <row r="147" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A147" s="24">
         <f>IF(B147="","",SUBTOTAL(3,$B$4:B147))</f>
         <v>144</v>
@@ -38060,7 +38095,7 @@
       <c r="BC147" s="71"/>
       <c r="BD147" s="71"/>
     </row>
-    <row r="148" spans="1:56">
+    <row r="148" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A148" s="24">
         <f>IF(B148="","",SUBTOTAL(3,$B$4:B148))</f>
         <v>145</v>
@@ -38178,7 +38213,7 @@
       <c r="BC148" s="71"/>
       <c r="BD148" s="71"/>
     </row>
-    <row r="149" spans="1:56">
+    <row r="149" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A149" s="24">
         <f>IF(B149="","",SUBTOTAL(3,$B$4:B149))</f>
         <v>146</v>
@@ -38296,7 +38331,7 @@
       <c r="BC149" s="71"/>
       <c r="BD149" s="71"/>
     </row>
-    <row r="150" spans="1:56">
+    <row r="150" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A150" s="24">
         <f>IF(B150="","",SUBTOTAL(3,$B$4:B150))</f>
         <v>147</v>
@@ -38414,7 +38449,7 @@
       <c r="BC150" s="71"/>
       <c r="BD150" s="71"/>
     </row>
-    <row r="151" spans="1:56">
+    <row r="151" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A151" s="24">
         <f>IF(B151="","",SUBTOTAL(3,$B$4:B151))</f>
         <v>148</v>
@@ -38532,7 +38567,7 @@
       <c r="BC151" s="71"/>
       <c r="BD151" s="71"/>
     </row>
-    <row r="152" spans="1:56">
+    <row r="152" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A152" s="24">
         <f>IF(B152="","",SUBTOTAL(3,$B$4:B152))</f>
         <v>149</v>
@@ -38650,7 +38685,7 @@
       <c r="BC152" s="71"/>
       <c r="BD152" s="71"/>
     </row>
-    <row r="153" spans="1:56">
+    <row r="153" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A153" s="24">
         <f>IF(B153="","",SUBTOTAL(3,$B$4:B153))</f>
         <v>150</v>
@@ -38768,7 +38803,7 @@
       <c r="BC153" s="71"/>
       <c r="BD153" s="71"/>
     </row>
-    <row r="154" spans="1:56">
+    <row r="154" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A154" s="24">
         <f>IF(B154="","",SUBTOTAL(3,$B$4:B154))</f>
         <v>151</v>
@@ -38886,7 +38921,7 @@
       <c r="BC154" s="71"/>
       <c r="BD154" s="71"/>
     </row>
-    <row r="155" spans="1:56">
+    <row r="155" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A155" s="24">
         <f>IF(B155="","",SUBTOTAL(3,$B$4:B155))</f>
         <v>152</v>
@@ -39004,7 +39039,7 @@
       <c r="BC155" s="71"/>
       <c r="BD155" s="71"/>
     </row>
-    <row r="156" spans="1:56">
+    <row r="156" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A156" s="24">
         <f>IF(B156="","",SUBTOTAL(3,$B$4:B156))</f>
         <v>153</v>
@@ -39122,7 +39157,7 @@
       <c r="BC156" s="71"/>
       <c r="BD156" s="71"/>
     </row>
-    <row r="157" spans="1:56">
+    <row r="157" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A157" s="24">
         <f>IF(B157="","",SUBTOTAL(3,$B$4:B157))</f>
         <v>154</v>
@@ -39240,7 +39275,7 @@
       <c r="BC157" s="71"/>
       <c r="BD157" s="71"/>
     </row>
-    <row r="158" spans="1:56">
+    <row r="158" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A158" s="24">
         <f>IF(B158="","",SUBTOTAL(3,$B$4:B158))</f>
         <v>155</v>
@@ -39358,7 +39393,7 @@
       <c r="BC158" s="71"/>
       <c r="BD158" s="71"/>
     </row>
-    <row r="159" spans="1:56">
+    <row r="159" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A159" s="24">
         <f>IF(B159="","",SUBTOTAL(3,$B$4:B159))</f>
         <v>156</v>
@@ -39476,7 +39511,7 @@
       <c r="BC159" s="71"/>
       <c r="BD159" s="71"/>
     </row>
-    <row r="160" spans="1:56">
+    <row r="160" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A160" s="24">
         <f>IF(B160="","",SUBTOTAL(3,$B$4:B160))</f>
         <v>157</v>
@@ -39594,7 +39629,7 @@
       <c r="BC160" s="71"/>
       <c r="BD160" s="71"/>
     </row>
-    <row r="161" spans="1:56">
+    <row r="161" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A161" s="24">
         <f>IF(B161="","",SUBTOTAL(3,$B$4:B161))</f>
         <v>158</v>
@@ -39712,7 +39747,7 @@
       <c r="BC161" s="71"/>
       <c r="BD161" s="71"/>
     </row>
-    <row r="162" spans="1:56">
+    <row r="162" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A162" s="24">
         <f>IF(B162="","",SUBTOTAL(3,$B$4:B162))</f>
         <v>159</v>
@@ -39830,7 +39865,7 @@
       <c r="BC162" s="71"/>
       <c r="BD162" s="71"/>
     </row>
-    <row r="163" spans="1:56">
+    <row r="163" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A163" s="24">
         <f>IF(B163="","",SUBTOTAL(3,$B$4:B163))</f>
         <v>160</v>
@@ -39948,7 +39983,7 @@
       <c r="BC163" s="71"/>
       <c r="BD163" s="71"/>
     </row>
-    <row r="164" spans="1:56">
+    <row r="164" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A164" s="24">
         <f>IF(B164="","",SUBTOTAL(3,$B$4:B164))</f>
         <v>161</v>
@@ -40066,7 +40101,7 @@
       <c r="BC164" s="71"/>
       <c r="BD164" s="71"/>
     </row>
-    <row r="165" spans="1:56">
+    <row r="165" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A165" s="24">
         <f>IF(B165="","",SUBTOTAL(3,$B$4:B165))</f>
         <v>162</v>
@@ -40184,7 +40219,7 @@
       <c r="BC165" s="71"/>
       <c r="BD165" s="71"/>
     </row>
-    <row r="166" spans="1:56">
+    <row r="166" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A166" s="24">
         <f>IF(B166="","",SUBTOTAL(3,$B$4:B166))</f>
         <v>163</v>
@@ -40302,7 +40337,7 @@
       <c r="BC166" s="71"/>
       <c r="BD166" s="71"/>
     </row>
-    <row r="167" spans="1:56">
+    <row r="167" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A167" s="24">
         <f>IF(B167="","",SUBTOTAL(3,$B$4:B167))</f>
         <v>164</v>
@@ -40420,7 +40455,7 @@
       <c r="BC167" s="71"/>
       <c r="BD167" s="71"/>
     </row>
-    <row r="168" spans="1:56">
+    <row r="168" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A168" s="24">
         <f>IF(B168="","",SUBTOTAL(3,$B$4:B168))</f>
         <v>165</v>
@@ -40538,7 +40573,7 @@
       <c r="BC168" s="71"/>
       <c r="BD168" s="71"/>
     </row>
-    <row r="169" spans="1:56">
+    <row r="169" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A169" s="24">
         <f>IF(B169="","",SUBTOTAL(3,$B$4:B169))</f>
         <v>166</v>
@@ -40656,7 +40691,7 @@
       <c r="BC169" s="71"/>
       <c r="BD169" s="71"/>
     </row>
-    <row r="170" spans="1:56">
+    <row r="170" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A170" s="24">
         <f>IF(B170="","",SUBTOTAL(3,$B$4:B170))</f>
         <v>167</v>
@@ -40774,7 +40809,7 @@
       <c r="BC170" s="71"/>
       <c r="BD170" s="71"/>
     </row>
-    <row r="171" spans="1:56">
+    <row r="171" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A171" s="24">
         <f>IF(B171="","",SUBTOTAL(3,$B$4:B171))</f>
         <v>168</v>
@@ -40892,7 +40927,7 @@
       <c r="BC171" s="71"/>
       <c r="BD171" s="71"/>
     </row>
-    <row r="172" spans="1:56">
+    <row r="172" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A172" s="24">
         <f>IF(B172="","",SUBTOTAL(3,$B$4:B172))</f>
         <v>169</v>
@@ -41010,7 +41045,7 @@
       <c r="BC172" s="71"/>
       <c r="BD172" s="71"/>
     </row>
-    <row r="173" spans="1:56">
+    <row r="173" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A173" s="24">
         <f>IF(B173="","",SUBTOTAL(3,$B$4:B173))</f>
         <v>170</v>
@@ -41128,7 +41163,7 @@
       <c r="BC173" s="71"/>
       <c r="BD173" s="71"/>
     </row>
-    <row r="174" spans="1:56">
+    <row r="174" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A174" s="24">
         <f>IF(B174="","",SUBTOTAL(3,$B$4:B174))</f>
         <v>171</v>
@@ -41246,7 +41281,7 @@
       <c r="BC174" s="71"/>
       <c r="BD174" s="71"/>
     </row>
-    <row r="175" spans="1:56">
+    <row r="175" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A175" s="24">
         <f>IF(B175="","",SUBTOTAL(3,$B$4:B175))</f>
         <v>172</v>
@@ -41364,7 +41399,7 @@
       <c r="BC175" s="71"/>
       <c r="BD175" s="71"/>
     </row>
-    <row r="176" spans="1:56">
+    <row r="176" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A176" s="24">
         <f>IF(B176="","",SUBTOTAL(3,$B$4:B176))</f>
         <v>173</v>
@@ -41482,7 +41517,7 @@
       <c r="BC176" s="71"/>
       <c r="BD176" s="71"/>
     </row>
-    <row r="177" spans="1:56">
+    <row r="177" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A177" s="24">
         <f>IF(B177="","",SUBTOTAL(3,$B$4:B177))</f>
         <v>174</v>
@@ -41600,7 +41635,7 @@
       <c r="BC177" s="71"/>
       <c r="BD177" s="71"/>
     </row>
-    <row r="178" spans="1:56">
+    <row r="178" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A178" s="24">
         <f>IF(B178="","",SUBTOTAL(3,$B$4:B178))</f>
         <v>175</v>
@@ -41726,7 +41761,7 @@
       <c r="BC178" s="71"/>
       <c r="BD178" s="71"/>
     </row>
-    <row r="179" spans="1:56">
+    <row r="179" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A179" s="24">
         <f>IF(B179="","",SUBTOTAL(3,$B$4:B179))</f>
         <v>176</v>
@@ -41852,7 +41887,7 @@
       <c r="BC179" s="71"/>
       <c r="BD179" s="71"/>
     </row>
-    <row r="180" spans="1:56">
+    <row r="180" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A180" s="24">
         <f>IF(B180="","",SUBTOTAL(3,$B$4:B180))</f>
         <v>177</v>
@@ -41978,7 +42013,7 @@
       <c r="BC180" s="71"/>
       <c r="BD180" s="71"/>
     </row>
-    <row r="181" spans="1:56">
+    <row r="181" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A181" s="24">
         <f>IF(B181="","",SUBTOTAL(3,$B$4:B181))</f>
         <v>178</v>
@@ -42104,7 +42139,7 @@
       <c r="BC181" s="71"/>
       <c r="BD181" s="71"/>
     </row>
-    <row r="182" spans="1:56">
+    <row r="182" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A182" s="24">
         <f>IF(B182="","",SUBTOTAL(3,$B$4:B182))</f>
         <v>179</v>
@@ -42171,11 +42206,11 @@
       <c r="AD182" s="54"/>
       <c r="AE182" s="31">
         <f t="shared" si="38"/>
-        <v>151.35</v>
+        <v>272.43</v>
       </c>
       <c r="AF182" s="32">
         <f t="shared" si="39"/>
-        <v>151.35</v>
+        <v>30.269999999999982</v>
       </c>
       <c r="AG182" s="30"/>
       <c r="AH182" s="33"/>
@@ -42193,11 +42228,15 @@
         <f t="shared" si="41"/>
         <v>302.7</v>
       </c>
-      <c r="AM182" s="35"/>
-      <c r="AN182" s="30"/>
+      <c r="AM182" s="35">
+        <v>46295</v>
+      </c>
+      <c r="AN182" s="30">
+        <v>2</v>
+      </c>
       <c r="AO182" s="36">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>302.7</v>
       </c>
       <c r="AP182" s="35"/>
       <c r="AQ182" s="30"/>
@@ -42226,7 +42265,7 @@
       <c r="BC182" s="71"/>
       <c r="BD182" s="71"/>
     </row>
-    <row r="183" spans="1:56">
+    <row r="183" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A183" s="24">
         <f>IF(B183="","",SUBTOTAL(3,$B$4:B183))</f>
         <v>180</v>
@@ -42293,11 +42332,11 @@
       <c r="AD183" s="54"/>
       <c r="AE183" s="31">
         <f t="shared" si="38"/>
-        <v>148.44999999999999</v>
+        <v>267.20999999999998</v>
       </c>
       <c r="AF183" s="32">
         <f t="shared" si="39"/>
-        <v>148.44999999999999</v>
+        <v>29.689999999999998</v>
       </c>
       <c r="AG183" s="30"/>
       <c r="AH183" s="33"/>
@@ -42315,11 +42354,15 @@
         <f t="shared" si="41"/>
         <v>296.89999999999998</v>
       </c>
-      <c r="AM183" s="35"/>
-      <c r="AN183" s="30"/>
+      <c r="AM183" s="35">
+        <v>46295</v>
+      </c>
+      <c r="AN183" s="30">
+        <v>2</v>
+      </c>
       <c r="AO183" s="36">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>296.89999999999998</v>
       </c>
       <c r="AP183" s="35"/>
       <c r="AQ183" s="30"/>
@@ -42348,7 +42391,7 @@
       <c r="BC183" s="71"/>
       <c r="BD183" s="71"/>
     </row>
-    <row r="184" spans="1:56">
+    <row r="184" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A184" s="24">
         <f>IF(B184="","",SUBTOTAL(3,$B$4:B184))</f>
         <v>181</v>
@@ -42466,7 +42509,7 @@
       <c r="BC184" s="71"/>
       <c r="BD184" s="71"/>
     </row>
-    <row r="185" spans="1:56">
+    <row r="185" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A185" s="24">
         <f>IF(B185="","",SUBTOTAL(3,$B$4:B185))</f>
         <v>182</v>
@@ -42584,7 +42627,7 @@
       <c r="BC185" s="71"/>
       <c r="BD185" s="71"/>
     </row>
-    <row r="186" spans="1:56">
+    <row r="186" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A186" s="24">
         <f>IF(B186="","",SUBTOTAL(3,$B$4:B186))</f>
         <v>183</v>
@@ -42702,7 +42745,7 @@
       <c r="BC186" s="71"/>
       <c r="BD186" s="71"/>
     </row>
-    <row r="187" spans="1:56">
+    <row r="187" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A187" s="24">
         <f>IF(B187="","",SUBTOTAL(3,$B$4:B187))</f>
         <v>184</v>
@@ -42820,7 +42863,7 @@
       <c r="BC187" s="71"/>
       <c r="BD187" s="71"/>
     </row>
-    <row r="188" spans="1:56">
+    <row r="188" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A188" s="24">
         <f>IF(B188="","",SUBTOTAL(3,$B$4:B188))</f>
         <v>185</v>
@@ -42938,7 +42981,7 @@
       <c r="BC188" s="71"/>
       <c r="BD188" s="71"/>
     </row>
-    <row r="189" spans="1:56">
+    <row r="189" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A189" s="24">
         <f>IF(B189="","",SUBTOTAL(3,$B$4:B189))</f>
         <v>186</v>
@@ -43056,7 +43099,7 @@
       <c r="BC189" s="71"/>
       <c r="BD189" s="71"/>
     </row>
-    <row r="190" spans="1:56">
+    <row r="190" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A190" s="24">
         <f>IF(B190="","",SUBTOTAL(3,$B$4:B190))</f>
         <v>187</v>
@@ -43174,7 +43217,7 @@
       <c r="BC190" s="71"/>
       <c r="BD190" s="71"/>
     </row>
-    <row r="191" spans="1:56">
+    <row r="191" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A191" s="24">
         <f>IF(B191="","",SUBTOTAL(3,$B$4:B191))</f>
         <v>188</v>
@@ -43292,7 +43335,7 @@
       <c r="BC191" s="71"/>
       <c r="BD191" s="71"/>
     </row>
-    <row r="192" spans="1:56">
+    <row r="192" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A192" s="24">
         <f>IF(B192="","",SUBTOTAL(3,$B$4:B192))</f>
         <v>189</v>
@@ -43410,7 +43453,7 @@
       <c r="BC192" s="71"/>
       <c r="BD192" s="71"/>
     </row>
-    <row r="193" spans="1:56">
+    <row r="193" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A193" s="24">
         <f>IF(B193="","",SUBTOTAL(3,$B$4:B193))</f>
         <v>190</v>
@@ -43528,7 +43571,7 @@
       <c r="BC193" s="71"/>
       <c r="BD193" s="71"/>
     </row>
-    <row r="194" spans="1:56">
+    <row r="194" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A194" s="24">
         <f>IF(B194="","",SUBTOTAL(3,$B$4:B194))</f>
         <v>191</v>
@@ -43646,7 +43689,7 @@
       <c r="BC194" s="71"/>
       <c r="BD194" s="71"/>
     </row>
-    <row r="195" spans="1:56">
+    <row r="195" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A195" s="24">
         <f>IF(B195="","",SUBTOTAL(3,$B$4:B195))</f>
         <v>192</v>
@@ -43764,7 +43807,7 @@
       <c r="BC195" s="71"/>
       <c r="BD195" s="71"/>
     </row>
-    <row r="196" spans="1:56">
+    <row r="196" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A196" s="24">
         <f>IF(B196="","",SUBTOTAL(3,$B$4:B196))</f>
         <v>193</v>
@@ -43882,7 +43925,7 @@
       <c r="BC196" s="71"/>
       <c r="BD196" s="71"/>
     </row>
-    <row r="197" spans="1:56">
+    <row r="197" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A197" s="24">
         <f>IF(B197="","",SUBTOTAL(3,$B$4:B197))</f>
         <v>194</v>
@@ -44000,7 +44043,7 @@
       <c r="BC197" s="71"/>
       <c r="BD197" s="71"/>
     </row>
-    <row r="198" spans="1:56">
+    <row r="198" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A198" s="24">
         <f>IF(B198="","",SUBTOTAL(3,$B$4:B198))</f>
         <v>195</v>
@@ -44118,7 +44161,7 @@
       <c r="BC198" s="71"/>
       <c r="BD198" s="71"/>
     </row>
-    <row r="199" spans="1:56">
+    <row r="199" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A199" s="24">
         <f>IF(B199="","",SUBTOTAL(3,$B$4:B199))</f>
         <v>196</v>
@@ -44236,7 +44279,7 @@
       <c r="BC199" s="71"/>
       <c r="BD199" s="71"/>
     </row>
-    <row r="200" spans="1:56">
+    <row r="200" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A200" s="24">
         <f>IF(B200="","",SUBTOTAL(3,$B$4:B200))</f>
         <v>197</v>
@@ -44354,7 +44397,7 @@
       <c r="BC200" s="71"/>
       <c r="BD200" s="71"/>
     </row>
-    <row r="201" spans="1:56">
+    <row r="201" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A201" s="24">
         <f>IF(B201="","",SUBTOTAL(3,$B$4:B201))</f>
         <v>198</v>
@@ -44472,7 +44515,7 @@
       <c r="BC201" s="71"/>
       <c r="BD201" s="71"/>
     </row>
-    <row r="202" spans="1:56">
+    <row r="202" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A202" s="24">
         <f>IF(B202="","",SUBTOTAL(3,$B$4:B202))</f>
         <v>199</v>
@@ -44590,7 +44633,7 @@
       <c r="BC202" s="71"/>
       <c r="BD202" s="71"/>
     </row>
-    <row r="203" spans="1:56">
+    <row r="203" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A203" s="24">
         <f>IF(B203="","",SUBTOTAL(3,$B$4:B203))</f>
         <v>200</v>
@@ -44708,7 +44751,7 @@
       <c r="BC203" s="71"/>
       <c r="BD203" s="71"/>
     </row>
-    <row r="204" spans="1:56">
+    <row r="204" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A204" s="24">
         <f>IF(B204="","",SUBTOTAL(3,$B$4:B204))</f>
         <v>201</v>
@@ -44826,7 +44869,7 @@
       <c r="BC204" s="71"/>
       <c r="BD204" s="71"/>
     </row>
-    <row r="205" spans="1:56">
+    <row r="205" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A205" s="24">
         <f>IF(B205="","",SUBTOTAL(3,$B$4:B205))</f>
         <v>202</v>
@@ -44944,7 +44987,7 @@
       <c r="BC205" s="71"/>
       <c r="BD205" s="71"/>
     </row>
-    <row r="206" spans="1:56">
+    <row r="206" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A206" s="24">
         <f>IF(B206="","",SUBTOTAL(3,$B$4:B206))</f>
         <v>203</v>
@@ -45062,7 +45105,7 @@
       <c r="BC206" s="71"/>
       <c r="BD206" s="71"/>
     </row>
-    <row r="207" spans="1:56">
+    <row r="207" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A207" s="24">
         <f>IF(B207="","",SUBTOTAL(3,$B$4:B207))</f>
         <v>204</v>
@@ -45180,7 +45223,7 @@
       <c r="BC207" s="71"/>
       <c r="BD207" s="71"/>
     </row>
-    <row r="208" spans="1:56">
+    <row r="208" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A208" s="24">
         <f>IF(B208="","",SUBTOTAL(3,$B$4:B208))</f>
         <v>205</v>
@@ -45298,7 +45341,7 @@
       <c r="BC208" s="71"/>
       <c r="BD208" s="71"/>
     </row>
-    <row r="209" spans="1:56">
+    <row r="209" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A209" s="24">
         <f>IF(B209="","",SUBTOTAL(3,$B$4:B209))</f>
         <v>206</v>
@@ -45416,7 +45459,7 @@
       <c r="BC209" s="71"/>
       <c r="BD209" s="71"/>
     </row>
-    <row r="210" spans="1:56">
+    <row r="210" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A210" s="24">
         <f>IF(B210="","",SUBTOTAL(3,$B$4:B210))</f>
         <v>207</v>
@@ -45534,7 +45577,7 @@
       <c r="BC210" s="71"/>
       <c r="BD210" s="71"/>
     </row>
-    <row r="211" spans="1:56">
+    <row r="211" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A211" s="24">
         <f>IF(B211="","",SUBTOTAL(3,$B$4:B211))</f>
         <v>208</v>
@@ -45652,7 +45695,7 @@
       <c r="BC211" s="71"/>
       <c r="BD211" s="71"/>
     </row>
-    <row r="212" spans="1:56">
+    <row r="212" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A212" s="24">
         <f>IF(B212="","",SUBTOTAL(3,$B$4:B212))</f>
         <v>209</v>
@@ -45770,7 +45813,7 @@
       <c r="BC212" s="71"/>
       <c r="BD212" s="71"/>
     </row>
-    <row r="213" spans="1:56">
+    <row r="213" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A213" s="24">
         <f>IF(B213="","",SUBTOTAL(3,$B$4:B213))</f>
         <v>210</v>
@@ -45888,7 +45931,7 @@
       <c r="BC213" s="71"/>
       <c r="BD213" s="71"/>
     </row>
-    <row r="214" spans="1:56">
+    <row r="214" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A214" s="24">
         <f>IF(B214="","",SUBTOTAL(3,$B$4:B214))</f>
         <v>211</v>
@@ -46006,7 +46049,7 @@
       <c r="BC214" s="71"/>
       <c r="BD214" s="71"/>
     </row>
-    <row r="215" spans="1:56">
+    <row r="215" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A215" s="24">
         <f>IF(B215="","",SUBTOTAL(3,$B$4:B215))</f>
         <v>212</v>
@@ -46124,7 +46167,7 @@
       <c r="BC215" s="71"/>
       <c r="BD215" s="71"/>
     </row>
-    <row r="216" spans="1:56">
+    <row r="216" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A216" s="24">
         <f>IF(B216="","",SUBTOTAL(3,$B$4:B216))</f>
         <v>213</v>
@@ -46242,7 +46285,7 @@
       <c r="BC216" s="71"/>
       <c r="BD216" s="71"/>
     </row>
-    <row r="217" spans="1:56">
+    <row r="217" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A217" s="24">
         <f>IF(B217="","",SUBTOTAL(3,$B$4:B217))</f>
         <v>214</v>
@@ -46360,7 +46403,7 @@
       <c r="BC217" s="71"/>
       <c r="BD217" s="71"/>
     </row>
-    <row r="218" spans="1:56">
+    <row r="218" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A218" s="24">
         <f>IF(B218="","",SUBTOTAL(3,$B$4:B218))</f>
         <v>215</v>
@@ -46478,7 +46521,7 @@
       <c r="BC218" s="71"/>
       <c r="BD218" s="71"/>
     </row>
-    <row r="219" spans="1:56">
+    <row r="219" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A219" s="24">
         <f>IF(B219="","",SUBTOTAL(3,$B$4:B219))</f>
         <v>216</v>
@@ -46596,7 +46639,7 @@
       <c r="BC219" s="71"/>
       <c r="BD219" s="71"/>
     </row>
-    <row r="220" spans="1:56">
+    <row r="220" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A220" s="24">
         <f>IF(B220="","",SUBTOTAL(3,$B$4:B220))</f>
         <v>217</v>
@@ -46714,7 +46757,7 @@
       <c r="BC220" s="71"/>
       <c r="BD220" s="71"/>
     </row>
-    <row r="221" spans="1:56">
+    <row r="221" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A221" s="24">
         <f>IF(B221="","",SUBTOTAL(3,$B$4:B221))</f>
         <v>218</v>
@@ -46832,7 +46875,7 @@
       <c r="BC221" s="71"/>
       <c r="BD221" s="71"/>
     </row>
-    <row r="222" spans="1:56">
+    <row r="222" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A222" s="24">
         <f>IF(B222="","",SUBTOTAL(3,$B$4:B222))</f>
         <v>219</v>
@@ -46950,7 +46993,7 @@
       <c r="BC222" s="71"/>
       <c r="BD222" s="71"/>
     </row>
-    <row r="223" spans="1:56">
+    <row r="223" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A223" s="24">
         <f>IF(B223="","",SUBTOTAL(3,$B$4:B223))</f>
         <v>220</v>
@@ -47068,7 +47111,7 @@
       <c r="BC223" s="71"/>
       <c r="BD223" s="71"/>
     </row>
-    <row r="224" spans="1:56">
+    <row r="224" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A224" s="24">
         <f>IF(B224="","",SUBTOTAL(3,$B$4:B224))</f>
         <v>221</v>
@@ -47186,7 +47229,7 @@
       <c r="BC224" s="71"/>
       <c r="BD224" s="71"/>
     </row>
-    <row r="225" spans="1:56">
+    <row r="225" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A225" s="24">
         <f>IF(B225="","",SUBTOTAL(3,$B$4:B225))</f>
         <v>222</v>
@@ -47304,7 +47347,7 @@
       <c r="BC225" s="71"/>
       <c r="BD225" s="71"/>
     </row>
-    <row r="226" spans="1:56">
+    <row r="226" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A226" s="24">
         <f>IF(B226="","",SUBTOTAL(3,$B$4:B226))</f>
         <v>223</v>
@@ -47422,7 +47465,7 @@
       <c r="BC226" s="71"/>
       <c r="BD226" s="71"/>
     </row>
-    <row r="227" spans="1:56">
+    <row r="227" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A227" s="24">
         <f>IF(B227="","",SUBTOTAL(3,$B$4:B227))</f>
         <v>224</v>
@@ -47540,7 +47583,7 @@
       <c r="BC227" s="71"/>
       <c r="BD227" s="71"/>
     </row>
-    <row r="228" spans="1:56">
+    <row r="228" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A228" s="24">
         <f>IF(B228="","",SUBTOTAL(3,$B$4:B228))</f>
         <v>225</v>
@@ -47658,7 +47701,7 @@
       <c r="BC228" s="71"/>
       <c r="BD228" s="71"/>
     </row>
-    <row r="229" spans="1:56">
+    <row r="229" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A229" s="24">
         <f>IF(B229="","",SUBTOTAL(3,$B$4:B229))</f>
         <v>226</v>
@@ -47776,7 +47819,7 @@
       <c r="BC229" s="71"/>
       <c r="BD229" s="71"/>
     </row>
-    <row r="230" spans="1:56">
+    <row r="230" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A230" s="24">
         <f>IF(B230="","",SUBTOTAL(3,$B$4:B230))</f>
         <v>227</v>
@@ -47894,7 +47937,7 @@
       <c r="BC230" s="71"/>
       <c r="BD230" s="71"/>
     </row>
-    <row r="231" spans="1:56">
+    <row r="231" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A231" s="24">
         <f>IF(B231="","",SUBTOTAL(3,$B$4:B231))</f>
         <v>228</v>
@@ -48012,7 +48055,7 @@
       <c r="BC231" s="71"/>
       <c r="BD231" s="71"/>
     </row>
-    <row r="232" spans="1:56">
+    <row r="232" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A232" s="24">
         <f>IF(B232="","",SUBTOTAL(3,$B$4:B232))</f>
         <v>229</v>
@@ -48130,7 +48173,7 @@
       <c r="BC232" s="71"/>
       <c r="BD232" s="71"/>
     </row>
-    <row r="233" spans="1:56">
+    <row r="233" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A233" s="24">
         <f>IF(B233="","",SUBTOTAL(3,$B$4:B233))</f>
         <v>230</v>
@@ -48248,7 +48291,7 @@
       <c r="BC233" s="71"/>
       <c r="BD233" s="71"/>
     </row>
-    <row r="234" spans="1:56">
+    <row r="234" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A234" s="24">
         <f>IF(B234="","",SUBTOTAL(3,$B$4:B234))</f>
         <v>231</v>
@@ -48366,7 +48409,7 @@
       <c r="BC234" s="71"/>
       <c r="BD234" s="71"/>
     </row>
-    <row r="235" spans="1:56">
+    <row r="235" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A235" s="24">
         <f>IF(B235="","",SUBTOTAL(3,$B$4:B235))</f>
         <v>232</v>
@@ -48492,7 +48535,7 @@
       <c r="BC235" s="71"/>
       <c r="BD235" s="71"/>
     </row>
-    <row r="236" spans="1:56">
+    <row r="236" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A236" s="24">
         <f>IF(B236="","",SUBTOTAL(3,$B$4:B236))</f>
         <v>233</v>
@@ -48618,7 +48661,7 @@
       <c r="BC236" s="71"/>
       <c r="BD236" s="71"/>
     </row>
-    <row r="237" spans="1:56">
+    <row r="237" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A237" s="24">
         <f>IF(B237="","",SUBTOTAL(3,$B$4:B237))</f>
         <v>234</v>
@@ -48744,7 +48787,7 @@
       <c r="BC237" s="71"/>
       <c r="BD237" s="71"/>
     </row>
-    <row r="238" spans="1:56">
+    <row r="238" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A238" s="24">
         <f>IF(B238="","",SUBTOTAL(3,$B$4:B238))</f>
         <v>235</v>
@@ -48870,7 +48913,7 @@
       <c r="BC238" s="71"/>
       <c r="BD238" s="71"/>
     </row>
-    <row r="239" spans="1:56">
+    <row r="239" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A239" s="24">
         <f>IF(B239="","",SUBTOTAL(3,$B$4:B239))</f>
         <v>236</v>
@@ -48996,7 +49039,7 @@
       <c r="BC239" s="71"/>
       <c r="BD239" s="71"/>
     </row>
-    <row r="240" spans="1:56">
+    <row r="240" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A240" s="24">
         <f>IF(B240="","",SUBTOTAL(3,$B$4:B240))</f>
         <v>237</v>
@@ -49122,7 +49165,7 @@
       <c r="BC240" s="71"/>
       <c r="BD240" s="71"/>
     </row>
-    <row r="241" spans="1:56">
+    <row r="241" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A241" s="24">
         <f>IF(B241="","",SUBTOTAL(3,$B$4:B241))</f>
         <v>238</v>
@@ -49248,7 +49291,7 @@
       <c r="BC241" s="71"/>
       <c r="BD241" s="71"/>
     </row>
-    <row r="242" spans="1:56">
+    <row r="242" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A242" s="24">
         <f>IF(B242="","",SUBTOTAL(3,$B$4:B242))</f>
         <v>239</v>
@@ -49374,7 +49417,7 @@
       <c r="BC242" s="71"/>
       <c r="BD242" s="71"/>
     </row>
-    <row r="243" spans="1:56">
+    <row r="243" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A243" s="24">
         <f>IF(B243="","",SUBTOTAL(3,$B$4:B243))</f>
         <v>240</v>
@@ -49500,7 +49543,7 @@
       <c r="BC243" s="71"/>
       <c r="BD243" s="71"/>
     </row>
-    <row r="244" spans="1:56">
+    <row r="244" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A244" s="24">
         <f>IF(B244="","",SUBTOTAL(3,$B$4:B244))</f>
         <v>241</v>
@@ -49626,7 +49669,7 @@
       <c r="BC244" s="71"/>
       <c r="BD244" s="71"/>
     </row>
-    <row r="245" spans="1:56">
+    <row r="245" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A245" s="24">
         <f>IF(B245="","",SUBTOTAL(3,$B$4:B245))</f>
         <v>242</v>
@@ -49752,7 +49795,7 @@
       <c r="BC245" s="71"/>
       <c r="BD245" s="71"/>
     </row>
-    <row r="246" spans="1:56">
+    <row r="246" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A246" s="24">
         <f>IF(B246="","",SUBTOTAL(3,$B$4:B246))</f>
         <v>243</v>
@@ -49870,21 +49913,27 @@
         <f t="shared" si="53"/>
         <v>3463.5</v>
       </c>
-      <c r="AW246" s="35"/>
-      <c r="AX246" s="30"/>
+      <c r="AW246" s="35">
+        <v>46295</v>
+      </c>
+      <c r="AX246" s="30">
+        <v>1</v>
+      </c>
       <c r="AY246" s="32">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>3463.5</v>
       </c>
       <c r="AZ246" s="30" t="s">
         <v>440</v>
       </c>
-      <c r="BA246" s="63"/>
+      <c r="BA246" s="63" t="s">
+        <v>872</v>
+      </c>
       <c r="BB246" s="71"/>
       <c r="BC246" s="71"/>
       <c r="BD246" s="71"/>
     </row>
-    <row r="247" spans="1:56">
+    <row r="247" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A247" s="24">
         <f>IF(B247="","",SUBTOTAL(3,$B$4:B247))</f>
         <v>244</v>
@@ -50010,7 +50059,7 @@
       <c r="BC247" s="71"/>
       <c r="BD247" s="71"/>
     </row>
-    <row r="248" spans="1:56">
+    <row r="248" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A248" s="24">
         <f>IF(B248="","",SUBTOTAL(3,$B$4:B248))</f>
         <v>245</v>
@@ -50148,7 +50197,7 @@
       <c r="BC248" s="71"/>
       <c r="BD248" s="71"/>
     </row>
-    <row r="249" spans="1:56">
+    <row r="249" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A249" s="24">
         <f>IF(B249="","",SUBTOTAL(3,$B$4:B249))</f>
         <v>246</v>
@@ -50274,7 +50323,7 @@
       <c r="BC249" s="71"/>
       <c r="BD249" s="71"/>
     </row>
-    <row r="250" spans="1:56">
+    <row r="250" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A250" s="24">
         <f>IF(B250="","",SUBTOTAL(3,$B$4:B250))</f>
         <v>247</v>
@@ -50400,7 +50449,7 @@
       <c r="BC250" s="71"/>
       <c r="BD250" s="71"/>
     </row>
-    <row r="251" spans="1:56">
+    <row r="251" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A251" s="24">
         <f>IF(B251="","",SUBTOTAL(3,$B$4:B251))</f>
         <v>248</v>
@@ -50526,7 +50575,7 @@
       <c r="BC251" s="71"/>
       <c r="BD251" s="71"/>
     </row>
-    <row r="252" spans="1:56">
+    <row r="252" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A252" s="24">
         <f>IF(B252="","",SUBTOTAL(3,$B$4:B252))</f>
         <v>249</v>
@@ -50652,7 +50701,7 @@
       <c r="BC252" s="71"/>
       <c r="BD252" s="71"/>
     </row>
-    <row r="253" spans="1:56">
+    <row r="253" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A253" s="24">
         <f>IF(B253="","",SUBTOTAL(3,$B$4:B253))</f>
         <v>250</v>
@@ -50778,7 +50827,7 @@
       <c r="BC253" s="71"/>
       <c r="BD253" s="71"/>
     </row>
-    <row r="254" spans="1:56">
+    <row r="254" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A254" s="24">
         <f>IF(B254="","",SUBTOTAL(3,$B$4:B254))</f>
         <v>251</v>
@@ -50904,7 +50953,7 @@
       <c r="BC254" s="71"/>
       <c r="BD254" s="71"/>
     </row>
-    <row r="255" spans="1:56">
+    <row r="255" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A255" s="24">
         <f>IF(B255="","",SUBTOTAL(3,$B$4:B255))</f>
         <v>252</v>
@@ -51030,7 +51079,7 @@
       <c r="BC255" s="71"/>
       <c r="BD255" s="71"/>
     </row>
-    <row r="256" spans="1:56">
+    <row r="256" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A256" s="24">
         <f>IF(B256="","",SUBTOTAL(3,$B$4:B256))</f>
         <v>253</v>
@@ -51156,7 +51205,7 @@
       <c r="BC256" s="71"/>
       <c r="BD256" s="71"/>
     </row>
-    <row r="257" spans="1:56">
+    <row r="257" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A257" s="24">
         <f>IF(B257="","",SUBTOTAL(3,$B$4:B257))</f>
         <v>254</v>
@@ -51223,11 +51272,11 @@
       <c r="AD257" s="54"/>
       <c r="AE257" s="31">
         <f t="shared" si="47"/>
-        <v>1423.8</v>
+        <v>2562.84</v>
       </c>
       <c r="AF257" s="32">
         <f t="shared" si="48"/>
-        <v>1423.8</v>
+        <v>284.75999999999976</v>
       </c>
       <c r="AG257" s="30"/>
       <c r="AH257" s="33"/>
@@ -51245,11 +51294,15 @@
         <f t="shared" si="50"/>
         <v>2847.6</v>
       </c>
-      <c r="AM257" s="35"/>
-      <c r="AN257" s="30"/>
+      <c r="AM257" s="35">
+        <v>46293</v>
+      </c>
+      <c r="AN257" s="30">
+        <v>1</v>
+      </c>
       <c r="AO257" s="36">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2847.6</v>
       </c>
       <c r="AP257" s="35"/>
       <c r="AQ257" s="30"/>
@@ -51278,7 +51331,7 @@
       <c r="BC257" s="71"/>
       <c r="BD257" s="71"/>
     </row>
-    <row r="258" spans="1:56">
+    <row r="258" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A258" s="24">
         <f>IF(B258="","",SUBTOTAL(3,$B$4:B258))</f>
         <v>255</v>
@@ -51345,11 +51398,11 @@
       <c r="AD258" s="54"/>
       <c r="AE258" s="31">
         <f t="shared" si="47"/>
-        <v>1411.2</v>
+        <v>2540.16</v>
       </c>
       <c r="AF258" s="32">
         <f t="shared" si="48"/>
-        <v>1411.2</v>
+        <v>282.24000000000024</v>
       </c>
       <c r="AG258" s="30"/>
       <c r="AH258" s="33"/>
@@ -51367,11 +51420,15 @@
         <f t="shared" si="50"/>
         <v>2822.4</v>
       </c>
-      <c r="AM258" s="35"/>
-      <c r="AN258" s="30"/>
+      <c r="AM258" s="35">
+        <v>46293</v>
+      </c>
+      <c r="AN258" s="30">
+        <v>1</v>
+      </c>
       <c r="AO258" s="36">
-        <f t="shared" si="51"/>
-        <v>0</v>
+        <f t="shared" ref="AO258" si="58">IFERROR(AN258*$P258/$N258,0)</f>
+        <v>2822.4</v>
       </c>
       <c r="AP258" s="35"/>
       <c r="AQ258" s="30"/>
@@ -51400,7 +51457,7 @@
       <c r="BC258" s="71"/>
       <c r="BD258" s="71"/>
     </row>
-    <row r="259" spans="1:56">
+    <row r="259" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A259" s="24">
         <f>IF(B259="","",SUBTOTAL(3,$B$4:B259))</f>
         <v>256</v>
@@ -51526,7 +51583,7 @@
       <c r="BC259" s="71"/>
       <c r="BD259" s="71"/>
     </row>
-    <row r="260" spans="1:56">
+    <row r="260" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A260" s="24">
         <f>IF(B260="","",SUBTOTAL(3,$B$4:B260))</f>
         <v>257</v>
@@ -51651,7 +51708,7 @@
         <v>1</v>
       </c>
       <c r="AY260" s="32">
-        <f t="shared" ref="AY260" si="58">IFERROR(AX260*$P260/$N260,0)</f>
+        <f t="shared" ref="AY260" si="59">IFERROR(AX260*$P260/$N260,0)</f>
         <v>677.6</v>
       </c>
       <c r="AZ260" s="30" t="s">
@@ -51664,7 +51721,7 @@
       <c r="BC260" s="71"/>
       <c r="BD260" s="71"/>
     </row>
-    <row r="261" spans="1:56">
+    <row r="261" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A261" s="24">
         <f>IF(B261="","",SUBTOTAL(3,$B$4:B261))</f>
         <v>258</v>
@@ -51802,7 +51859,7 @@
       <c r="BC261" s="71"/>
       <c r="BD261" s="71"/>
     </row>
-    <row r="262" spans="1:56">
+    <row r="262" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A262" s="24">
         <f>IF(B262="","",SUBTOTAL(3,$B$4:B262))</f>
         <v>259</v>
@@ -51927,7 +51984,7 @@
         <v>2</v>
       </c>
       <c r="AY262" s="32">
-        <f t="shared" ref="AY262:AY263" si="59">IFERROR(AX262*$P262/$N262,0)</f>
+        <f t="shared" ref="AY262:AY263" si="60">IFERROR(AX262*$P262/$N262,0)</f>
         <v>964.9</v>
       </c>
       <c r="AZ262" s="30" t="s">
@@ -51940,7 +51997,7 @@
       <c r="BC262" s="71"/>
       <c r="BD262" s="71"/>
     </row>
-    <row r="263" spans="1:56">
+    <row r="263" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A263" s="24">
         <f>IF(B263="","",SUBTOTAL(3,$B$4:B263))</f>
         <v>260</v>
@@ -52065,7 +52122,7 @@
         <v>1</v>
       </c>
       <c r="AY263" s="32">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>500.3</v>
       </c>
       <c r="AZ263" s="30" t="s">
@@ -52078,7 +52135,7 @@
       <c r="BC263" s="71"/>
       <c r="BD263" s="71"/>
     </row>
-    <row r="264" spans="1:56">
+    <row r="264" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A264" s="24">
         <f>IF(B264="","",SUBTOTAL(3,$B$4:B264))</f>
         <v>261</v>
@@ -52087,7 +52144,7 @@
         <v>439</v>
       </c>
       <c r="C264" s="25" t="str">
-        <f t="shared" ref="C264:C292" si="60">D264&amp;" "&amp;E264</f>
+        <f t="shared" ref="C264:C292" si="61">D264&amp;" "&amp;E264</f>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D264" s="25" t="s">
@@ -52208,7 +52265,7 @@
       <c r="BC264" s="71"/>
       <c r="BD264" s="71"/>
     </row>
-    <row r="265" spans="1:56">
+    <row r="265" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A265" s="24">
         <f>IF(B265="","",SUBTOTAL(3,$B$4:B265))</f>
         <v>262</v>
@@ -52217,7 +52274,7 @@
         <v>439</v>
       </c>
       <c r="C265" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D265" s="25" t="s">
@@ -52278,17 +52335,17 @@
       <c r="AC265" s="30"/>
       <c r="AD265" s="54"/>
       <c r="AE265" s="31">
-        <f t="shared" ref="AE265:AE268" si="61">+AL265*0.5+AO265*0.4+AV265*0.1</f>
+        <f t="shared" ref="AE265:AE268" si="62">+AL265*0.5+AO265*0.4+AV265*0.1</f>
         <v>950.04</v>
       </c>
       <c r="AF265" s="32">
-        <f t="shared" ref="AF265:AF268" si="62">+P265-AE265</f>
+        <f t="shared" ref="AF265:AF268" si="63">+P265-AE265</f>
         <v>105.55999999999995</v>
       </c>
       <c r="AG265" s="30"/>
       <c r="AH265" s="33"/>
       <c r="AI265" s="34">
-        <f t="shared" ref="AI265:AI268" si="63">+AH265*P265</f>
+        <f t="shared" ref="AI265:AI268" si="64">+AH265*P265</f>
         <v>0</v>
       </c>
       <c r="AJ265" s="35">
@@ -52298,7 +52355,7 @@
         <v>28</v>
       </c>
       <c r="AL265" s="36">
-        <f t="shared" ref="AL265:AL268" si="64">IFERROR(AK265*$P265/$N265,0)</f>
+        <f t="shared" ref="AL265:AL268" si="65">IFERROR(AK265*$P265/$N265,0)</f>
         <v>1055.5999999999999</v>
       </c>
       <c r="AM265" s="35">
@@ -52308,26 +52365,26 @@
         <v>28</v>
       </c>
       <c r="AO265" s="36">
-        <f t="shared" ref="AO265:AO268" si="65">IFERROR(AN265*$P265/$N265,0)</f>
+        <f t="shared" ref="AO265:AO268" si="66">IFERROR(AN265*$P265/$N265,0)</f>
         <v>1055.5999999999999</v>
       </c>
       <c r="AP265" s="35"/>
       <c r="AQ265" s="30"/>
       <c r="AR265" s="36">
-        <f t="shared" ref="AR265:AR268" si="66">IFERROR(AQ265*$P265/$N265,0)</f>
+        <f t="shared" ref="AR265:AR268" si="67">IFERROR(AQ265*$P265/$N265,0)</f>
         <v>0</v>
       </c>
       <c r="AS265" s="27"/>
       <c r="AT265" s="37"/>
       <c r="AU265" s="30"/>
       <c r="AV265" s="36">
-        <f t="shared" ref="AV265:AV268" si="67">IFERROR(AU265*$P265/$N265,0)</f>
+        <f t="shared" ref="AV265:AV268" si="68">IFERROR(AU265*$P265/$N265,0)</f>
         <v>0</v>
       </c>
       <c r="AW265" s="35"/>
       <c r="AX265" s="30"/>
       <c r="AY265" s="32">
-        <f t="shared" ref="AY265:AY268" si="68">IFERROR(AX265*$P265/$N265,0)</f>
+        <f t="shared" ref="AY265:AY268" si="69">IFERROR(AX265*$P265/$N265,0)</f>
         <v>0</v>
       </c>
       <c r="AZ265" s="30" t="s">
@@ -52338,7 +52395,7 @@
       <c r="BC265" s="71"/>
       <c r="BD265" s="71"/>
     </row>
-    <row r="266" spans="1:56">
+    <row r="266" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A266" s="24">
         <f>IF(B266="","",SUBTOTAL(3,$B$4:B266))</f>
         <v>263</v>
@@ -52347,7 +52404,7 @@
         <v>439</v>
       </c>
       <c r="C266" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D266" s="25" t="s">
@@ -52408,17 +52465,17 @@
       <c r="AC266" s="30"/>
       <c r="AD266" s="54"/>
       <c r="AE266" s="31">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>98.910000000000011</v>
       </c>
       <c r="AF266" s="32">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>10.989999999999995</v>
       </c>
       <c r="AG266" s="30"/>
       <c r="AH266" s="33"/>
       <c r="AI266" s="34">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AJ266" s="35">
@@ -52428,7 +52485,7 @@
         <v>10</v>
       </c>
       <c r="AL266" s="36">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>109.9</v>
       </c>
       <c r="AM266" s="35">
@@ -52438,26 +52495,26 @@
         <v>10</v>
       </c>
       <c r="AO266" s="36">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>109.9</v>
       </c>
       <c r="AP266" s="35"/>
       <c r="AQ266" s="30"/>
       <c r="AR266" s="36">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AS266" s="27"/>
       <c r="AT266" s="37"/>
       <c r="AU266" s="30"/>
       <c r="AV266" s="36">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AW266" s="35"/>
       <c r="AX266" s="30"/>
       <c r="AY266" s="32">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="AZ266" s="30" t="s">
@@ -52468,7 +52525,7 @@
       <c r="BC266" s="71"/>
       <c r="BD266" s="71"/>
     </row>
-    <row r="267" spans="1:56">
+    <row r="267" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A267" s="24">
         <f>IF(B267="","",SUBTOTAL(3,$B$4:B267))</f>
         <v>264</v>
@@ -52477,7 +52534,7 @@
         <v>439</v>
       </c>
       <c r="C267" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D267" s="25" t="s">
@@ -52538,17 +52595,17 @@
       <c r="AC267" s="30"/>
       <c r="AD267" s="54"/>
       <c r="AE267" s="31">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1730.88</v>
       </c>
       <c r="AF267" s="32">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>192.31999999999994</v>
       </c>
       <c r="AG267" s="30"/>
       <c r="AH267" s="33"/>
       <c r="AI267" s="34">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AJ267" s="35">
@@ -52558,7 +52615,7 @@
         <v>25</v>
       </c>
       <c r="AL267" s="36">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>1923.2</v>
       </c>
       <c r="AM267" s="35">
@@ -52568,26 +52625,26 @@
         <v>25</v>
       </c>
       <c r="AO267" s="36">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>1923.2</v>
       </c>
       <c r="AP267" s="35"/>
       <c r="AQ267" s="30"/>
       <c r="AR267" s="36">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AS267" s="27"/>
       <c r="AT267" s="37"/>
       <c r="AU267" s="30"/>
       <c r="AV267" s="36">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AW267" s="35"/>
       <c r="AX267" s="30"/>
       <c r="AY267" s="32">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="AZ267" s="30" t="s">
@@ -52598,7 +52655,7 @@
       <c r="BC267" s="71"/>
       <c r="BD267" s="71"/>
     </row>
-    <row r="268" spans="1:56">
+    <row r="268" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A268" s="24">
         <f>IF(B268="","",SUBTOTAL(3,$B$4:B268))</f>
         <v>265</v>
@@ -52607,7 +52664,7 @@
         <v>439</v>
       </c>
       <c r="C268" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D268" s="25" t="s">
@@ -52668,17 +52725,17 @@
       <c r="AC268" s="30"/>
       <c r="AD268" s="54"/>
       <c r="AE268" s="31">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>349.74</v>
       </c>
       <c r="AF268" s="32">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>38.860000000000014</v>
       </c>
       <c r="AG268" s="30"/>
       <c r="AH268" s="33"/>
       <c r="AI268" s="34">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AJ268" s="35">
@@ -52688,7 +52745,7 @@
         <v>10</v>
       </c>
       <c r="AL268" s="36">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>388.6</v>
       </c>
       <c r="AM268" s="35">
@@ -52698,26 +52755,26 @@
         <v>10</v>
       </c>
       <c r="AO268" s="36">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>388.6</v>
       </c>
       <c r="AP268" s="35"/>
       <c r="AQ268" s="30"/>
       <c r="AR268" s="36">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AS268" s="27"/>
       <c r="AT268" s="37"/>
       <c r="AU268" s="30"/>
       <c r="AV268" s="36">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AW268" s="35"/>
       <c r="AX268" s="30"/>
       <c r="AY268" s="32">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="AZ268" s="30" t="s">
@@ -52728,7 +52785,7 @@
       <c r="BC268" s="71"/>
       <c r="BD268" s="71"/>
     </row>
-    <row r="269" spans="1:56">
+    <row r="269" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A269" s="24">
         <f>IF(B269="","",SUBTOTAL(3,$B$4:B269))</f>
         <v>266</v>
@@ -52737,7 +52794,7 @@
         <v>439</v>
       </c>
       <c r="C269" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D269" s="25" t="s">
@@ -52798,17 +52855,17 @@
       <c r="AC269" s="30"/>
       <c r="AD269" s="54"/>
       <c r="AE269" s="31">
-        <f t="shared" ref="AE269:AE292" si="69">+AL269*0.5+AO269*0.4+AV269*0.1</f>
+        <f t="shared" ref="AE269:AE292" si="70">+AL269*0.5+AO269*0.4+AV269*0.1</f>
         <v>31.86</v>
       </c>
       <c r="AF269" s="32">
-        <f t="shared" ref="AF269:AF292" si="70">+P269-AE269</f>
+        <f t="shared" ref="AF269:AF292" si="71">+P269-AE269</f>
         <v>3.5399999999999991</v>
       </c>
       <c r="AG269" s="30"/>
       <c r="AH269" s="33"/>
       <c r="AI269" s="34">
-        <f t="shared" ref="AI269:AI292" si="71">+AH269*P269</f>
+        <f t="shared" ref="AI269:AI292" si="72">+AH269*P269</f>
         <v>0</v>
       </c>
       <c r="AJ269" s="35">
@@ -52818,7 +52875,7 @@
         <v>3</v>
       </c>
       <c r="AL269" s="36">
-        <f t="shared" ref="AL269:AL290" si="72">IFERROR(AK269*$P269/$N269,0)</f>
+        <f t="shared" ref="AL269:AL290" si="73">IFERROR(AK269*$P269/$N269,0)</f>
         <v>35.4</v>
       </c>
       <c r="AM269" s="35">
@@ -52828,26 +52885,26 @@
         <v>3</v>
       </c>
       <c r="AO269" s="36">
-        <f t="shared" ref="AO269:AO292" si="73">IFERROR(AN269*$P269/$N269,0)</f>
+        <f t="shared" ref="AO269:AO292" si="74">IFERROR(AN269*$P269/$N269,0)</f>
         <v>35.4</v>
       </c>
       <c r="AP269" s="35"/>
       <c r="AQ269" s="30"/>
       <c r="AR269" s="36">
-        <f t="shared" ref="AR269:AR292" si="74">IFERROR(AQ269*$P269/$N269,0)</f>
+        <f t="shared" ref="AR269:AR292" si="75">IFERROR(AQ269*$P269/$N269,0)</f>
         <v>0</v>
       </c>
       <c r="AS269" s="27"/>
       <c r="AT269" s="37"/>
       <c r="AU269" s="30"/>
       <c r="AV269" s="36">
-        <f t="shared" ref="AV269:AV292" si="75">IFERROR(AU269*$P269/$N269,0)</f>
+        <f t="shared" ref="AV269:AV292" si="76">IFERROR(AU269*$P269/$N269,0)</f>
         <v>0</v>
       </c>
       <c r="AW269" s="35"/>
       <c r="AX269" s="30"/>
       <c r="AY269" s="32">
-        <f t="shared" ref="AY269:AY292" si="76">IFERROR(AX269*$P269/$N269,0)</f>
+        <f t="shared" ref="AY269:AY292" si="77">IFERROR(AX269*$P269/$N269,0)</f>
         <v>0</v>
       </c>
       <c r="AZ269" s="30" t="s">
@@ -52858,7 +52915,7 @@
       <c r="BC269" s="71"/>
       <c r="BD269" s="71"/>
     </row>
-    <row r="270" spans="1:56">
+    <row r="270" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A270" s="24">
         <f>IF(B270="","",SUBTOTAL(3,$B$4:B270))</f>
         <v>267</v>
@@ -52867,7 +52924,7 @@
         <v>439</v>
       </c>
       <c r="C270" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D270" s="25" t="s">
@@ -52928,17 +52985,17 @@
       <c r="AC270" s="30"/>
       <c r="AD270" s="54"/>
       <c r="AE270" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>51.57</v>
       </c>
       <c r="AF270" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>5.7299999999999969</v>
       </c>
       <c r="AG270" s="30"/>
       <c r="AH270" s="33"/>
       <c r="AI270" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ270" s="35">
@@ -52948,7 +53005,7 @@
         <v>1</v>
       </c>
       <c r="AL270" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>57.3</v>
       </c>
       <c r="AM270" s="35">
@@ -52958,26 +53015,26 @@
         <v>1</v>
       </c>
       <c r="AO270" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>57.3</v>
       </c>
       <c r="AP270" s="35"/>
       <c r="AQ270" s="30"/>
       <c r="AR270" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS270" s="27"/>
       <c r="AT270" s="37"/>
       <c r="AU270" s="30"/>
       <c r="AV270" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW270" s="35"/>
       <c r="AX270" s="30"/>
       <c r="AY270" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ270" s="30" t="s">
@@ -52988,7 +53045,7 @@
       <c r="BC270" s="71"/>
       <c r="BD270" s="71"/>
     </row>
-    <row r="271" spans="1:56">
+    <row r="271" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A271" s="24">
         <f>IF(B271="","",SUBTOTAL(3,$B$4:B271))</f>
         <v>268</v>
@@ -52997,7 +53054,7 @@
         <v>439</v>
       </c>
       <c r="C271" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D271" s="25" t="s">
@@ -53058,17 +53115,17 @@
       <c r="AC271" s="30"/>
       <c r="AD271" s="54"/>
       <c r="AE271" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>361.71</v>
       </c>
       <c r="AF271" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>40.19</v>
       </c>
       <c r="AG271" s="30"/>
       <c r="AH271" s="33"/>
       <c r="AI271" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ271" s="35">
@@ -53078,7 +53135,7 @@
         <v>8</v>
       </c>
       <c r="AL271" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>401.9</v>
       </c>
       <c r="AM271" s="35">
@@ -53088,26 +53145,26 @@
         <v>8</v>
       </c>
       <c r="AO271" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>401.9</v>
       </c>
       <c r="AP271" s="35"/>
       <c r="AQ271" s="30"/>
       <c r="AR271" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS271" s="27"/>
       <c r="AT271" s="37"/>
       <c r="AU271" s="30"/>
       <c r="AV271" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW271" s="35"/>
       <c r="AX271" s="30"/>
       <c r="AY271" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ271" s="30" t="s">
@@ -53118,7 +53175,7 @@
       <c r="BC271" s="71"/>
       <c r="BD271" s="71"/>
     </row>
-    <row r="272" spans="1:56">
+    <row r="272" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A272" s="24">
         <f>IF(B272="","",SUBTOTAL(3,$B$4:B272))</f>
         <v>269</v>
@@ -53127,7 +53184,7 @@
         <v>439</v>
       </c>
       <c r="C272" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D272" s="25" t="s">
@@ -53188,17 +53245,17 @@
       <c r="AC272" s="30"/>
       <c r="AD272" s="54"/>
       <c r="AE272" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>30.96</v>
       </c>
       <c r="AF272" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>3.4399999999999977</v>
       </c>
       <c r="AG272" s="30"/>
       <c r="AH272" s="33"/>
       <c r="AI272" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ272" s="35">
@@ -53208,7 +53265,7 @@
         <v>1</v>
       </c>
       <c r="AL272" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>34.4</v>
       </c>
       <c r="AM272" s="35">
@@ -53218,26 +53275,26 @@
         <v>1</v>
       </c>
       <c r="AO272" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>34.4</v>
       </c>
       <c r="AP272" s="35"/>
       <c r="AQ272" s="30"/>
       <c r="AR272" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS272" s="27"/>
       <c r="AT272" s="37"/>
       <c r="AU272" s="30"/>
       <c r="AV272" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW272" s="35"/>
       <c r="AX272" s="30"/>
       <c r="AY272" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ272" s="30" t="s">
@@ -53248,7 +53305,7 @@
       <c r="BC272" s="71"/>
       <c r="BD272" s="71"/>
     </row>
-    <row r="273" spans="1:56">
+    <row r="273" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A273" s="24">
         <f>IF(B273="","",SUBTOTAL(3,$B$4:B273))</f>
         <v>270</v>
@@ -53257,7 +53314,7 @@
         <v>439</v>
       </c>
       <c r="C273" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D273" s="25" t="s">
@@ -53318,17 +53375,17 @@
       <c r="AC273" s="30"/>
       <c r="AD273" s="54"/>
       <c r="AE273" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>25.47</v>
       </c>
       <c r="AF273" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>2.8300000000000018</v>
       </c>
       <c r="AG273" s="30"/>
       <c r="AH273" s="33"/>
       <c r="AI273" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ273" s="35">
@@ -53338,7 +53395,7 @@
         <v>1</v>
       </c>
       <c r="AL273" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>28.3</v>
       </c>
       <c r="AM273" s="35">
@@ -53348,26 +53405,26 @@
         <v>1</v>
       </c>
       <c r="AO273" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>28.3</v>
       </c>
       <c r="AP273" s="35"/>
       <c r="AQ273" s="30"/>
       <c r="AR273" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS273" s="27"/>
       <c r="AT273" s="37"/>
       <c r="AU273" s="30"/>
       <c r="AV273" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW273" s="35"/>
       <c r="AX273" s="30"/>
       <c r="AY273" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ273" s="30" t="s">
@@ -53378,7 +53435,7 @@
       <c r="BC273" s="71"/>
       <c r="BD273" s="71"/>
     </row>
-    <row r="274" spans="1:56">
+    <row r="274" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A274" s="24">
         <f>IF(B274="","",SUBTOTAL(3,$B$4:B274))</f>
         <v>271</v>
@@ -53387,7 +53444,7 @@
         <v>439</v>
       </c>
       <c r="C274" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D274" s="25" t="s">
@@ -53448,17 +53505,17 @@
       <c r="AC274" s="30"/>
       <c r="AD274" s="54"/>
       <c r="AE274" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>25.56</v>
       </c>
       <c r="AF274" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>2.84</v>
       </c>
       <c r="AG274" s="30"/>
       <c r="AH274" s="33"/>
       <c r="AI274" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ274" s="35">
@@ -53468,7 +53525,7 @@
         <v>2</v>
       </c>
       <c r="AL274" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>28.4</v>
       </c>
       <c r="AM274" s="35">
@@ -53478,26 +53535,26 @@
         <v>2</v>
       </c>
       <c r="AO274" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>28.4</v>
       </c>
       <c r="AP274" s="35"/>
       <c r="AQ274" s="30"/>
       <c r="AR274" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS274" s="27"/>
       <c r="AT274" s="37"/>
       <c r="AU274" s="30"/>
       <c r="AV274" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW274" s="35"/>
       <c r="AX274" s="30"/>
       <c r="AY274" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ274" s="30" t="s">
@@ -53508,7 +53565,7 @@
       <c r="BC274" s="71"/>
       <c r="BD274" s="71"/>
     </row>
-    <row r="275" spans="1:56">
+    <row r="275" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A275" s="24">
         <f>IF(B275="","",SUBTOTAL(3,$B$4:B275))</f>
         <v>272</v>
@@ -53517,7 +53574,7 @@
         <v>439</v>
       </c>
       <c r="C275" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D275" s="25" t="s">
@@ -53578,17 +53635,17 @@
       <c r="AC275" s="30"/>
       <c r="AD275" s="54"/>
       <c r="AE275" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>19.89</v>
       </c>
       <c r="AF275" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>2.2100000000000009</v>
       </c>
       <c r="AG275" s="30"/>
       <c r="AH275" s="33"/>
       <c r="AI275" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ275" s="35">
@@ -53598,7 +53655,7 @@
         <v>1</v>
       </c>
       <c r="AL275" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>22.1</v>
       </c>
       <c r="AM275" s="35">
@@ -53608,26 +53665,26 @@
         <v>1</v>
       </c>
       <c r="AO275" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>22.1</v>
       </c>
       <c r="AP275" s="35"/>
       <c r="AQ275" s="30"/>
       <c r="AR275" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS275" s="27"/>
       <c r="AT275" s="37"/>
       <c r="AU275" s="30"/>
       <c r="AV275" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW275" s="35"/>
       <c r="AX275" s="30"/>
       <c r="AY275" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ275" s="30" t="s">
@@ -53638,7 +53695,7 @@
       <c r="BC275" s="71"/>
       <c r="BD275" s="71"/>
     </row>
-    <row r="276" spans="1:56">
+    <row r="276" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A276" s="24">
         <f>IF(B276="","",SUBTOTAL(3,$B$4:B276))</f>
         <v>273</v>
@@ -53647,7 +53704,7 @@
         <v>439</v>
       </c>
       <c r="C276" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D276" s="25" t="s">
@@ -53708,17 +53765,17 @@
       <c r="AC276" s="30"/>
       <c r="AD276" s="54"/>
       <c r="AE276" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>45.99</v>
       </c>
       <c r="AF276" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>5.1099999999999994</v>
       </c>
       <c r="AG276" s="30"/>
       <c r="AH276" s="33"/>
       <c r="AI276" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ276" s="35">
@@ -53728,7 +53785,7 @@
         <v>3</v>
       </c>
       <c r="AL276" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>51.1</v>
       </c>
       <c r="AM276" s="35">
@@ -53738,26 +53795,26 @@
         <v>3</v>
       </c>
       <c r="AO276" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>51.1</v>
       </c>
       <c r="AP276" s="35"/>
       <c r="AQ276" s="30"/>
       <c r="AR276" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS276" s="27"/>
       <c r="AT276" s="37"/>
       <c r="AU276" s="30"/>
       <c r="AV276" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW276" s="35"/>
       <c r="AX276" s="30"/>
       <c r="AY276" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ276" s="30" t="s">
@@ -53768,7 +53825,7 @@
       <c r="BC276" s="71"/>
       <c r="BD276" s="71"/>
     </row>
-    <row r="277" spans="1:56">
+    <row r="277" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A277" s="24">
         <f>IF(B277="","",SUBTOTAL(3,$B$4:B277))</f>
         <v>274</v>
@@ -53777,7 +53834,7 @@
         <v>439</v>
       </c>
       <c r="C277" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D277" s="25" t="s">
@@ -53838,17 +53895,17 @@
       <c r="AC277" s="30"/>
       <c r="AD277" s="54"/>
       <c r="AE277" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>56.519999999999996</v>
       </c>
       <c r="AF277" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>6.2800000000000011</v>
       </c>
       <c r="AG277" s="30"/>
       <c r="AH277" s="33"/>
       <c r="AI277" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ277" s="35">
@@ -53858,7 +53915,7 @@
         <v>1</v>
       </c>
       <c r="AL277" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>62.8</v>
       </c>
       <c r="AM277" s="35">
@@ -53868,26 +53925,26 @@
         <v>1</v>
       </c>
       <c r="AO277" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>62.8</v>
       </c>
       <c r="AP277" s="35"/>
       <c r="AQ277" s="30"/>
       <c r="AR277" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS277" s="27"/>
       <c r="AT277" s="37"/>
       <c r="AU277" s="30"/>
       <c r="AV277" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW277" s="35"/>
       <c r="AX277" s="30"/>
       <c r="AY277" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ277" s="30" t="s">
@@ -53898,7 +53955,7 @@
       <c r="BC277" s="71"/>
       <c r="BD277" s="71"/>
     </row>
-    <row r="278" spans="1:56">
+    <row r="278" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A278" s="24">
         <f>IF(B278="","",SUBTOTAL(3,$B$4:B278))</f>
         <v>275</v>
@@ -53907,7 +53964,7 @@
         <v>439</v>
       </c>
       <c r="C278" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D278" s="25" t="s">
@@ -53968,17 +54025,17 @@
       <c r="AC278" s="30"/>
       <c r="AD278" s="54"/>
       <c r="AE278" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>50.49</v>
       </c>
       <c r="AF278" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>5.6099999999999994</v>
       </c>
       <c r="AG278" s="30"/>
       <c r="AH278" s="33"/>
       <c r="AI278" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ278" s="35">
@@ -53988,7 +54045,7 @@
         <v>1</v>
       </c>
       <c r="AL278" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>56.1</v>
       </c>
       <c r="AM278" s="35">
@@ -53998,26 +54055,26 @@
         <v>1</v>
       </c>
       <c r="AO278" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>56.1</v>
       </c>
       <c r="AP278" s="35"/>
       <c r="AQ278" s="30"/>
       <c r="AR278" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS278" s="27"/>
       <c r="AT278" s="37"/>
       <c r="AU278" s="30"/>
       <c r="AV278" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW278" s="35"/>
       <c r="AX278" s="30"/>
       <c r="AY278" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ278" s="30" t="s">
@@ -54028,7 +54085,7 @@
       <c r="BC278" s="71"/>
       <c r="BD278" s="71"/>
     </row>
-    <row r="279" spans="1:56">
+    <row r="279" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A279" s="24">
         <f>IF(B279="","",SUBTOTAL(3,$B$4:B279))</f>
         <v>276</v>
@@ -54037,7 +54094,7 @@
         <v>439</v>
       </c>
       <c r="C279" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D279" s="25" t="s">
@@ -54098,17 +54155,17 @@
       <c r="AC279" s="30"/>
       <c r="AD279" s="54"/>
       <c r="AE279" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>29.25</v>
       </c>
       <c r="AF279" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>3.25</v>
       </c>
       <c r="AG279" s="30"/>
       <c r="AH279" s="33"/>
       <c r="AI279" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ279" s="35">
@@ -54118,7 +54175,7 @@
         <v>1</v>
       </c>
       <c r="AL279" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>32.5</v>
       </c>
       <c r="AM279" s="35">
@@ -54128,26 +54185,26 @@
         <v>1</v>
       </c>
       <c r="AO279" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>32.5</v>
       </c>
       <c r="AP279" s="35"/>
       <c r="AQ279" s="30"/>
       <c r="AR279" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS279" s="27"/>
       <c r="AT279" s="37"/>
       <c r="AU279" s="30"/>
       <c r="AV279" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW279" s="35"/>
       <c r="AX279" s="30"/>
       <c r="AY279" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ279" s="30" t="s">
@@ -54158,7 +54215,7 @@
       <c r="BC279" s="71"/>
       <c r="BD279" s="71"/>
     </row>
-    <row r="280" spans="1:56">
+    <row r="280" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A280" s="24">
         <f>IF(B280="","",SUBTOTAL(3,$B$4:B280))</f>
         <v>277</v>
@@ -54167,7 +54224,7 @@
         <v>439</v>
       </c>
       <c r="C280" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D280" s="25" t="s">
@@ -54228,17 +54285,17 @@
       <c r="AC280" s="30"/>
       <c r="AD280" s="54"/>
       <c r="AE280" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>339.12</v>
       </c>
       <c r="AF280" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>37.680000000000007</v>
       </c>
       <c r="AG280" s="30"/>
       <c r="AH280" s="33"/>
       <c r="AI280" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ280" s="35">
@@ -54248,7 +54305,7 @@
         <v>4</v>
       </c>
       <c r="AL280" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>376.8</v>
       </c>
       <c r="AM280" s="35">
@@ -54258,26 +54315,26 @@
         <v>4</v>
       </c>
       <c r="AO280" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>376.8</v>
       </c>
       <c r="AP280" s="35"/>
       <c r="AQ280" s="30"/>
       <c r="AR280" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS280" s="27"/>
       <c r="AT280" s="37"/>
       <c r="AU280" s="30"/>
       <c r="AV280" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW280" s="35"/>
       <c r="AX280" s="30"/>
       <c r="AY280" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ280" s="30" t="s">
@@ -54288,7 +54345,7 @@
       <c r="BC280" s="71"/>
       <c r="BD280" s="71"/>
     </row>
-    <row r="281" spans="1:56">
+    <row r="281" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A281" s="24">
         <f>IF(B281="","",SUBTOTAL(3,$B$4:B281))</f>
         <v>278</v>
@@ -54297,7 +54354,7 @@
         <v>439</v>
       </c>
       <c r="C281" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D281" s="25" t="s">
@@ -54358,17 +54415,17 @@
       <c r="AC281" s="30"/>
       <c r="AD281" s="54"/>
       <c r="AE281" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>55.71</v>
       </c>
       <c r="AF281" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>6.1899999999999977</v>
       </c>
       <c r="AG281" s="30"/>
       <c r="AH281" s="33"/>
       <c r="AI281" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ281" s="35">
@@ -54378,7 +54435,7 @@
         <v>2</v>
       </c>
       <c r="AL281" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>61.9</v>
       </c>
       <c r="AM281" s="35">
@@ -54388,26 +54445,26 @@
         <v>2</v>
       </c>
       <c r="AO281" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>61.9</v>
       </c>
       <c r="AP281" s="35"/>
       <c r="AQ281" s="30"/>
       <c r="AR281" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS281" s="27"/>
       <c r="AT281" s="37"/>
       <c r="AU281" s="30"/>
       <c r="AV281" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW281" s="35"/>
       <c r="AX281" s="30"/>
       <c r="AY281" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ281" s="30" t="s">
@@ -54418,7 +54475,7 @@
       <c r="BC281" s="71"/>
       <c r="BD281" s="71"/>
     </row>
-    <row r="282" spans="1:56">
+    <row r="282" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A282" s="24">
         <f>IF(B282="","",SUBTOTAL(3,$B$4:B282))</f>
         <v>279</v>
@@ -54427,7 +54484,7 @@
         <v>439</v>
       </c>
       <c r="C282" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D282" s="25" t="s">
@@ -54488,17 +54545,17 @@
       <c r="AC282" s="30"/>
       <c r="AD282" s="54"/>
       <c r="AE282" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>96.75</v>
       </c>
       <c r="AF282" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>10.75</v>
       </c>
       <c r="AG282" s="30"/>
       <c r="AH282" s="33"/>
       <c r="AI282" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ282" s="35">
@@ -54508,7 +54565,7 @@
         <v>2</v>
       </c>
       <c r="AL282" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>107.5</v>
       </c>
       <c r="AM282" s="35">
@@ -54518,26 +54575,26 @@
         <v>2</v>
       </c>
       <c r="AO282" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>107.5</v>
       </c>
       <c r="AP282" s="35"/>
       <c r="AQ282" s="30"/>
       <c r="AR282" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS282" s="27"/>
       <c r="AT282" s="37"/>
       <c r="AU282" s="30"/>
       <c r="AV282" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW282" s="35"/>
       <c r="AX282" s="30"/>
       <c r="AY282" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ282" s="30" t="s">
@@ -54548,7 +54605,7 @@
       <c r="BC282" s="71"/>
       <c r="BD282" s="71"/>
     </row>
-    <row r="283" spans="1:56">
+    <row r="283" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A283" s="24">
         <f>IF(B283="","",SUBTOTAL(3,$B$4:B283))</f>
         <v>280</v>
@@ -54557,7 +54614,7 @@
         <v>439</v>
       </c>
       <c r="C283" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D283" s="25" t="s">
@@ -54618,17 +54675,17 @@
       <c r="AC283" s="30"/>
       <c r="AD283" s="54"/>
       <c r="AE283" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>38.430000000000007</v>
       </c>
       <c r="AF283" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>4.269999999999996</v>
       </c>
       <c r="AG283" s="30"/>
       <c r="AH283" s="33"/>
       <c r="AI283" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ283" s="35">
@@ -54638,7 +54695,7 @@
         <v>1</v>
       </c>
       <c r="AL283" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>42.7</v>
       </c>
       <c r="AM283" s="35">
@@ -54648,26 +54705,26 @@
         <v>1</v>
       </c>
       <c r="AO283" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>42.7</v>
       </c>
       <c r="AP283" s="35"/>
       <c r="AQ283" s="30"/>
       <c r="AR283" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS283" s="27"/>
       <c r="AT283" s="37"/>
       <c r="AU283" s="30"/>
       <c r="AV283" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW283" s="35"/>
       <c r="AX283" s="30"/>
       <c r="AY283" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ283" s="30" t="s">
@@ -54678,7 +54735,7 @@
       <c r="BC283" s="71"/>
       <c r="BD283" s="71"/>
     </row>
-    <row r="284" spans="1:56">
+    <row r="284" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A284" s="24">
         <f>IF(B284="","",SUBTOTAL(3,$B$4:B284))</f>
         <v>281</v>
@@ -54687,7 +54744,7 @@
         <v>439</v>
       </c>
       <c r="C284" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D284" s="25" t="s">
@@ -54748,17 +54805,17 @@
       <c r="AC284" s="30"/>
       <c r="AD284" s="54"/>
       <c r="AE284" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>445.23</v>
       </c>
       <c r="AF284" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>49.46999999999997</v>
       </c>
       <c r="AG284" s="30"/>
       <c r="AH284" s="33"/>
       <c r="AI284" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ284" s="35">
@@ -54768,7 +54825,7 @@
         <v>2</v>
       </c>
       <c r="AL284" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>494.7</v>
       </c>
       <c r="AM284" s="35">
@@ -54778,26 +54835,26 @@
         <v>2</v>
       </c>
       <c r="AO284" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>494.7</v>
       </c>
       <c r="AP284" s="35"/>
       <c r="AQ284" s="30"/>
       <c r="AR284" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS284" s="27"/>
       <c r="AT284" s="37"/>
       <c r="AU284" s="30"/>
       <c r="AV284" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW284" s="35"/>
       <c r="AX284" s="30"/>
       <c r="AY284" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ284" s="30" t="s">
@@ -54808,7 +54865,7 @@
       <c r="BC284" s="71"/>
       <c r="BD284" s="71"/>
     </row>
-    <row r="285" spans="1:56">
+    <row r="285" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A285" s="24">
         <f>IF(B285="","",SUBTOTAL(3,$B$4:B285))</f>
         <v>282</v>
@@ -54817,7 +54874,7 @@
         <v>439</v>
       </c>
       <c r="C285" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D285" s="25" t="s">
@@ -54878,17 +54935,17 @@
       <c r="AC285" s="30"/>
       <c r="AD285" s="54"/>
       <c r="AE285" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>208.8</v>
       </c>
       <c r="AF285" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>23.199999999999989</v>
       </c>
       <c r="AG285" s="30"/>
       <c r="AH285" s="33"/>
       <c r="AI285" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ285" s="35">
@@ -54898,7 +54955,7 @@
         <v>1</v>
       </c>
       <c r="AL285" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>232</v>
       </c>
       <c r="AM285" s="35">
@@ -54908,26 +54965,26 @@
         <v>1</v>
       </c>
       <c r="AO285" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>232</v>
       </c>
       <c r="AP285" s="35"/>
       <c r="AQ285" s="30"/>
       <c r="AR285" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS285" s="27"/>
       <c r="AT285" s="37"/>
       <c r="AU285" s="30"/>
       <c r="AV285" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW285" s="35"/>
       <c r="AX285" s="30"/>
       <c r="AY285" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ285" s="30" t="s">
@@ -54938,7 +54995,7 @@
       <c r="BC285" s="71"/>
       <c r="BD285" s="71"/>
     </row>
-    <row r="286" spans="1:56">
+    <row r="286" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A286" s="24">
         <f>IF(B286="","",SUBTOTAL(3,$B$4:B286))</f>
         <v>283</v>
@@ -54947,7 +55004,7 @@
         <v>439</v>
       </c>
       <c r="C286" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D286" s="25" t="s">
@@ -55008,17 +55065,17 @@
       <c r="AC286" s="30"/>
       <c r="AD286" s="54"/>
       <c r="AE286" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>208.8</v>
       </c>
       <c r="AF286" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>23.199999999999989</v>
       </c>
       <c r="AG286" s="30"/>
       <c r="AH286" s="33"/>
       <c r="AI286" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ286" s="35">
@@ -55028,7 +55085,7 @@
         <v>1</v>
       </c>
       <c r="AL286" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>232</v>
       </c>
       <c r="AM286" s="35">
@@ -55038,26 +55095,26 @@
         <v>1</v>
       </c>
       <c r="AO286" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>232</v>
       </c>
       <c r="AP286" s="35"/>
       <c r="AQ286" s="30"/>
       <c r="AR286" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS286" s="27"/>
       <c r="AT286" s="37"/>
       <c r="AU286" s="30"/>
       <c r="AV286" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW286" s="35"/>
       <c r="AX286" s="30"/>
       <c r="AY286" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ286" s="30" t="s">
@@ -55068,7 +55125,7 @@
       <c r="BC286" s="71"/>
       <c r="BD286" s="71"/>
     </row>
-    <row r="287" spans="1:56">
+    <row r="287" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A287" s="24">
         <f>IF(B287="","",SUBTOTAL(3,$B$4:B287))</f>
         <v>284</v>
@@ -55077,7 +55134,7 @@
         <v>439</v>
       </c>
       <c r="C287" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D287" s="25" t="s">
@@ -55138,17 +55195,17 @@
       <c r="AC287" s="30"/>
       <c r="AD287" s="54"/>
       <c r="AE287" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>73.98</v>
       </c>
       <c r="AF287" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>8.2199999999999989</v>
       </c>
       <c r="AG287" s="30"/>
       <c r="AH287" s="33"/>
       <c r="AI287" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ287" s="35">
@@ -55158,7 +55215,7 @@
         <v>1</v>
       </c>
       <c r="AL287" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>82.2</v>
       </c>
       <c r="AM287" s="35">
@@ -55168,26 +55225,26 @@
         <v>1</v>
       </c>
       <c r="AO287" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>82.2</v>
       </c>
       <c r="AP287" s="35"/>
       <c r="AQ287" s="30"/>
       <c r="AR287" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS287" s="27"/>
       <c r="AT287" s="37"/>
       <c r="AU287" s="30"/>
       <c r="AV287" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW287" s="35"/>
       <c r="AX287" s="30"/>
       <c r="AY287" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ287" s="30" t="s">
@@ -55198,7 +55255,7 @@
       <c r="BC287" s="71"/>
       <c r="BD287" s="71"/>
     </row>
-    <row r="288" spans="1:56">
+    <row r="288" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A288" s="24">
         <f>IF(B288="","",SUBTOTAL(3,$B$4:B288))</f>
         <v>285</v>
@@ -55207,7 +55264,7 @@
         <v>439</v>
       </c>
       <c r="C288" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D288" s="25" t="s">
@@ -55268,17 +55325,17 @@
       <c r="AC288" s="30"/>
       <c r="AD288" s="54"/>
       <c r="AE288" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>75.78</v>
       </c>
       <c r="AF288" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>8.4200000000000017</v>
       </c>
       <c r="AG288" s="30"/>
       <c r="AH288" s="33"/>
       <c r="AI288" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ288" s="35">
@@ -55288,7 +55345,7 @@
         <v>1</v>
       </c>
       <c r="AL288" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>84.2</v>
       </c>
       <c r="AM288" s="35">
@@ -55298,26 +55355,26 @@
         <v>1</v>
       </c>
       <c r="AO288" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>84.2</v>
       </c>
       <c r="AP288" s="35"/>
       <c r="AQ288" s="30"/>
       <c r="AR288" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS288" s="27"/>
       <c r="AT288" s="37"/>
       <c r="AU288" s="30"/>
       <c r="AV288" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW288" s="35"/>
       <c r="AX288" s="30"/>
       <c r="AY288" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ288" s="30" t="s">
@@ -55328,7 +55385,7 @@
       <c r="BC288" s="71"/>
       <c r="BD288" s="71"/>
     </row>
-    <row r="289" spans="1:56">
+    <row r="289" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A289" s="24">
         <f>IF(B289="","",SUBTOTAL(3,$B$4:B289))</f>
         <v>286</v>
@@ -55337,7 +55394,7 @@
         <v>439</v>
       </c>
       <c r="C289" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D289" s="25" t="s">
@@ -55398,17 +55455,17 @@
       <c r="AC289" s="30"/>
       <c r="AD289" s="54"/>
       <c r="AE289" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>169.56</v>
       </c>
       <c r="AF289" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>18.840000000000003</v>
       </c>
       <c r="AG289" s="30"/>
       <c r="AH289" s="33"/>
       <c r="AI289" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ289" s="35">
@@ -55418,7 +55475,7 @@
         <v>2</v>
       </c>
       <c r="AL289" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>188.4</v>
       </c>
       <c r="AM289" s="35">
@@ -55428,26 +55485,26 @@
         <v>2</v>
       </c>
       <c r="AO289" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>188.4</v>
       </c>
       <c r="AP289" s="35"/>
       <c r="AQ289" s="30"/>
       <c r="AR289" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS289" s="27"/>
       <c r="AT289" s="37"/>
       <c r="AU289" s="30"/>
       <c r="AV289" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW289" s="35"/>
       <c r="AX289" s="30"/>
       <c r="AY289" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ289" s="30" t="s">
@@ -55458,7 +55515,7 @@
       <c r="BC289" s="71"/>
       <c r="BD289" s="71"/>
     </row>
-    <row r="290" spans="1:56">
+    <row r="290" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A290" s="24">
         <f>IF(B290="","",SUBTOTAL(3,$B$4:B290))</f>
         <v>287</v>
@@ -55467,7 +55524,7 @@
         <v>439</v>
       </c>
       <c r="C290" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D290" s="25" t="s">
@@ -55528,17 +55585,17 @@
       <c r="AC290" s="30"/>
       <c r="AD290" s="54"/>
       <c r="AE290" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>11.61</v>
       </c>
       <c r="AF290" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>1.2900000000000009</v>
       </c>
       <c r="AG290" s="30"/>
       <c r="AH290" s="33"/>
       <c r="AI290" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ290" s="35">
@@ -55548,7 +55605,7 @@
         <v>2</v>
       </c>
       <c r="AL290" s="36">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>12.9</v>
       </c>
       <c r="AM290" s="35">
@@ -55558,26 +55615,26 @@
         <v>2</v>
       </c>
       <c r="AO290" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>12.9</v>
       </c>
       <c r="AP290" s="35"/>
       <c r="AQ290" s="30"/>
       <c r="AR290" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS290" s="27"/>
       <c r="AT290" s="37"/>
       <c r="AU290" s="30"/>
       <c r="AV290" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW290" s="35"/>
       <c r="AX290" s="30"/>
       <c r="AY290" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ290" s="30" t="s">
@@ -55588,7 +55645,7 @@
       <c r="BC290" s="71"/>
       <c r="BD290" s="71"/>
     </row>
-    <row r="291" spans="1:56">
+    <row r="291" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A291" s="24">
         <f>IF(B291="","",SUBTOTAL(3,$B$4:B291))</f>
         <v>288</v>
@@ -55597,7 +55654,7 @@
         <v>439</v>
       </c>
       <c r="C291" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D291" s="25" t="s">
@@ -55658,17 +55715,17 @@
       <c r="AC291" s="30"/>
       <c r="AD291" s="54"/>
       <c r="AE291" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>217.53</v>
       </c>
       <c r="AF291" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>24.169999999999987</v>
       </c>
       <c r="AG291" s="30"/>
       <c r="AH291" s="33"/>
       <c r="AI291" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ291" s="35">
@@ -55678,7 +55735,7 @@
         <v>55</v>
       </c>
       <c r="AL291" s="36">
-        <f t="shared" ref="AL291:AL292" si="77">IFERROR(AK291*$P291/$N291,0)</f>
+        <f t="shared" ref="AL291:AL292" si="78">IFERROR(AK291*$P291/$N291,0)</f>
         <v>241.7</v>
       </c>
       <c r="AM291" s="35">
@@ -55688,26 +55745,26 @@
         <v>55</v>
       </c>
       <c r="AO291" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>241.7</v>
       </c>
       <c r="AP291" s="35"/>
       <c r="AQ291" s="30"/>
       <c r="AR291" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS291" s="27"/>
       <c r="AT291" s="37"/>
       <c r="AU291" s="30"/>
       <c r="AV291" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW291" s="35"/>
       <c r="AX291" s="30"/>
       <c r="AY291" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ291" s="30" t="s">
@@ -55718,7 +55775,7 @@
       <c r="BC291" s="71"/>
       <c r="BD291" s="71"/>
     </row>
-    <row r="292" spans="1:56">
+    <row r="292" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A292" s="24">
         <f>IF(B292="","",SUBTOTAL(3,$B$4:B292))</f>
         <v>289</v>
@@ -55727,7 +55784,7 @@
         <v>439</v>
       </c>
       <c r="C292" s="25" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>Shipment 2 Outlet Stack</v>
       </c>
       <c r="D292" s="25" t="s">
@@ -55788,17 +55845,17 @@
       <c r="AC292" s="30"/>
       <c r="AD292" s="54"/>
       <c r="AE292" s="31">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7.9200000000000008</v>
       </c>
       <c r="AF292" s="32">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.87999999999999989</v>
       </c>
       <c r="AG292" s="30"/>
       <c r="AH292" s="33"/>
       <c r="AI292" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AJ292" s="35">
@@ -55808,7 +55865,7 @@
         <v>2</v>
       </c>
       <c r="AL292" s="36">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="AM292" s="35">
@@ -55818,26 +55875,26 @@
         <v>2</v>
       </c>
       <c r="AO292" s="36">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="AP292" s="35"/>
       <c r="AQ292" s="30"/>
       <c r="AR292" s="36">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AS292" s="27"/>
       <c r="AT292" s="37"/>
       <c r="AU292" s="30"/>
       <c r="AV292" s="36">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AW292" s="35"/>
       <c r="AX292" s="30"/>
       <c r="AY292" s="32">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ292" s="30" t="s">
@@ -55848,7 +55905,7 @@
       <c r="BC292" s="71"/>
       <c r="BD292" s="71"/>
     </row>
-    <row r="293" spans="1:56">
+    <row r="293" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A293" s="24" t="str">
         <f>IF(B293="","",SUBTOTAL(3,$B$4:B293))</f>
         <v/>
@@ -55936,7 +55993,7 @@
       <c r="BC293" s="71"/>
       <c r="BD293" s="71"/>
     </row>
-    <row r="294" spans="1:56">
+    <row r="294" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A294" s="24" t="str">
         <f>IF(B294="","",SUBTOTAL(3,$B$4:B294))</f>
         <v/>
@@ -56024,7 +56081,7 @@
       <c r="BC294" s="71"/>
       <c r="BD294" s="71"/>
     </row>
-    <row r="295" spans="1:56">
+    <row r="295" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A295" s="24" t="str">
         <f>IF(B295="","",SUBTOTAL(3,$B$4:B295))</f>
         <v/>
@@ -56112,7 +56169,7 @@
       <c r="BC295" s="71"/>
       <c r="BD295" s="71"/>
     </row>
-    <row r="296" spans="1:56">
+    <row r="296" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A296" s="24" t="str">
         <f>IF(B296="","",SUBTOTAL(3,$B$4:B296))</f>
         <v/>
@@ -56200,7 +56257,7 @@
       <c r="BC296" s="71"/>
       <c r="BD296" s="71"/>
     </row>
-    <row r="297" spans="1:56">
+    <row r="297" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A297" s="24" t="str">
         <f>IF(B297="","",SUBTOTAL(3,$B$4:B297))</f>
         <v/>
@@ -56288,7 +56345,7 @@
       <c r="BC297" s="71"/>
       <c r="BD297" s="71"/>
     </row>
-    <row r="298" spans="1:56" ht="16.5" thickBot="1">
+    <row r="298" spans="1:56" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="38" t="str">
         <f>IF(B298="","",SUBTOTAL(3,$B$4:B298))</f>
         <v/>
@@ -56376,7 +56433,7 @@
       <c r="BC298" s="71"/>
       <c r="BD298" s="71"/>
     </row>
-    <row r="299" spans="1:56" ht="16.5" thickTop="1"/>
+    <row r="299" spans="1:56" ht="16.5" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A3:BD298" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}"/>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/03.QLDA/U284.xlsx
+++ b/03.QLDA/U284.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AMECC JSC\Amecc 2\00. Overall Report\03.QLDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F528CBA3-A77A-41D4-B8B1-8B9B74ADD471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A570CD-4AAB-4DEF-80D6-B242F656F65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,9 @@
     <definedName name="ㅋㅋㅋㅋㅋㅋㅋㅋㅋ" hidden="1">#REF!</definedName>
     <definedName name="ㅌㅊㅍㅌㅊㅍㅌㅋㅊㅍㅌ" hidden="1">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <pivotCaches>
-    <pivotCache cacheId="94" r:id="rId2"/>
+    <pivotCache cacheId="23" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3339,7 +3339,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46297.348200694447" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="295" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46302.405495254628" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="295" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A3:BA298" sheet="Progress"/>
   </cacheSource>
@@ -19753,7 +19753,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="94" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="BF3:BH8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="53">
     <pivotField showAll="0"/>
@@ -20343,7 +20343,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="51">
         <f ca="1">IF(WEEKDAY(TODAY()-1)=1,TODAY()-2,TODAY()-1)</f>
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="T2" s="13" t="s">
         <v>40</v>
